--- a/fv-copy-1000.xlsx
+++ b/fv-copy-1000.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>フォロワーを、笑顔に。</t>
+          <t>フォロワーを、喜びに。</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
@@ -872,7 +872,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>フォロワーを、喜びに。</t>
+          <t>フォロワーを、ハッピーに。</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -882,11 +882,11 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -895,7 +895,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>フォロワーを、ハッピーに。</t>
+          <t>フォロワーを、満足に。</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -905,11 +905,11 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -987,7 +987,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>お客様を、笑顔に。</t>
+          <t>お客様を、喜びに。</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E13" s="8" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>お客様を、喜びに。</t>
+          <t>お客様を、ハッピーに。</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1020,11 +1020,11 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>お客様を、ハッピーに。</t>
+          <t>お客様を、満足に。</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1043,11 +1043,11 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ファンを、笑顔に。</t>
+          <t>ファンを、喜びに。</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ファンを、喜びに。</t>
+          <t>ファンを、ハッピーに。</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>ファンを、ハッピーに。</t>
+          <t>ファンを、満足に。</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1181,11 +1181,11 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>商品を、笑顔に。</t>
+          <t>商品を、喜びに。</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E25" s="8" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>商品を、喜びに。</t>
+          <t>商品を、ハッピーに。</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1296,11 +1296,11 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>商品を、ハッピーに。</t>
+          <t>商品を、満足に。</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1319,11 +1319,11 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>売上を、笑顔に。</t>
+          <t>売上を、喜びに。</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>売上を、喜びに。</t>
+          <t>売上を、ハッピーに。</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E32" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>売上を、ハッピーに。</t>
+          <t>売上を、満足に。</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1457,11 +1457,11 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>数字を、笑顔に。</t>
+          <t>数字を、喜びに。</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>数字を、喜びに。</t>
+          <t>数字を、ハッピーに。</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -1572,11 +1572,11 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E38" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>数字を、ハッピーに。</t>
+          <t>数字を、満足に。</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>「好き」を、笑顔に。</t>
+          <t>「好き」を、喜びに。</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>「好き」を、喜びに。</t>
+          <t>「好き」を、ハッピーに。</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1710,11 +1710,11 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E44" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>「好き」を、ハッピーに。</t>
+          <t>「好き」を、満足に。</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1733,11 +1733,11 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>出会いを、笑顔に。</t>
+          <t>出会いを、喜びに。</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>出会いを、喜びに。</t>
+          <t>出会いを、ハッピーに。</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E50" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>出会いを、ハッピーに。</t>
+          <t>出会いを、満足に。</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1871,11 +1871,11 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E51" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>「いいね」を、笑顔に。</t>
+          <t>「いいね」を、喜びに。</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>「いいね」を、喜びに。</t>
+          <t>「いいね」を、ハッピーに。</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -1986,11 +1986,11 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E56" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>「いいね」を、ハッピーに。</t>
+          <t>「いいね」を、満足に。</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -2009,11 +2009,11 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E57" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>投稿を、笑顔に。</t>
+          <t>投稿を、喜びに。</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>投稿を、喜びに。</t>
+          <t>投稿を、ハッピーに。</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -2124,11 +2124,11 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E62" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>投稿を、ハッピーに。</t>
+          <t>投稿を、満足に。</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -2147,11 +2147,11 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>バズを、笑顔に。</t>
+          <t>バズを、喜びに。</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>バズを、喜びに。</t>
+          <t>バズを、ハッピーに。</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -2262,11 +2262,11 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E68" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>バズを、ハッピーに。</t>
+          <t>バズを、満足に。</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -2285,11 +2285,11 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>拡散を、笑顔に。</t>
+          <t>拡散を、喜びに。</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>拡散を、喜びに。</t>
+          <t>拡散を、ハッピーに。</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -2400,11 +2400,11 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E74" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>拡散を、ハッピーに。</t>
+          <t>拡散を、満足に。</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>フォロワーを、笑顔に変える。</t>
+          <t>フォロワーを、喜びに変える。</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E79" s="8" t="n">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>フォロワーを、喜びに変える。</t>
+          <t>フォロワーを、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -2538,11 +2538,11 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E80" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>フォロワーを、ハッピーに変える。</t>
+          <t>フォロワーを、満足に変える。</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -2561,11 +2561,11 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>お客様を、笑顔に変える。</t>
+          <t>お客様を、喜びに変える。</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E85" s="8" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>お客様を、喜びに変える。</t>
+          <t>お客様を、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -2676,11 +2676,11 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E86" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>お客様を、ハッピーに変える。</t>
+          <t>お客様を、満足に変える。</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -2699,11 +2699,11 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E87" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>ファンを、笑顔に変える。</t>
+          <t>ファンを、喜びに変える。</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E91" s="8" t="n">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>ファンを、喜びに変える。</t>
+          <t>ファンを、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -2814,11 +2814,11 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E92" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>ファンを、ハッピーに変える。</t>
+          <t>ファンを、満足に変える。</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -2837,11 +2837,11 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E93" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>商品を、笑顔に変える。</t>
+          <t>商品を、喜びに変える。</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E97" s="8" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>商品を、喜びに変える。</t>
+          <t>商品を、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -2952,11 +2952,11 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E98" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>商品を、ハッピーに変える。</t>
+          <t>商品を、満足に変える。</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -2975,11 +2975,11 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E99" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>売上を、笑顔に変える。</t>
+          <t>売上を、喜びに変える。</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E103" s="8" t="n">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>売上を、喜びに変える。</t>
+          <t>売上を、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -3090,11 +3090,11 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E104" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>売上を、ハッピーに変える。</t>
+          <t>売上を、満足に変える。</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -3113,11 +3113,11 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E105" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" ht="19" customHeight="1">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>数字を、笑顔に変える。</t>
+          <t>数字を、喜びに変える。</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E109" s="8" t="n">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>数字を、喜びに変える。</t>
+          <t>数字を、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -3228,11 +3228,11 @@
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E110" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" ht="19" customHeight="1">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>数字を、ハッピーに変える。</t>
+          <t>数字を、満足に変える。</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -3251,11 +3251,11 @@
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E111" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" ht="19" customHeight="1">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>「好き」を、笑顔に変える。</t>
+          <t>「好き」を、喜びに変える。</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E115" s="8" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>「好き」を、喜びに変える。</t>
+          <t>「好き」を、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -3366,11 +3366,11 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E116" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" ht="19" customHeight="1">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>「好き」を、ハッピーに変える。</t>
+          <t>「好き」を、満足に変える。</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -3389,11 +3389,11 @@
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E117" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>出会いを、笑顔に変える。</t>
+          <t>出会いを、喜びに変える。</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E121" s="8" t="n">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>出会いを、喜びに変える。</t>
+          <t>出会いを、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -3504,11 +3504,11 @@
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E122" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" ht="19" customHeight="1">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>出会いを、ハッピーに変える。</t>
+          <t>出会いを、満足に変える。</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -3527,11 +3527,11 @@
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E123" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" ht="19" customHeight="1">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>「いいね」を、笑顔に変える。</t>
+          <t>「いいね」を、喜びに変える。</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E127" s="8" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>「いいね」を、喜びに変える。</t>
+          <t>「いいね」を、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -3642,11 +3642,11 @@
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E128" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" ht="19" customHeight="1">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>「いいね」を、ハッピーに変える。</t>
+          <t>「いいね」を、満足に変える。</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -3665,11 +3665,11 @@
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E129" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" ht="19" customHeight="1">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>投稿を、笑顔に変える。</t>
+          <t>投稿を、喜びに変える。</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E133" s="8" t="n">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>投稿を、喜びに変える。</t>
+          <t>投稿を、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -3780,11 +3780,11 @@
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E134" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" ht="19" customHeight="1">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>投稿を、ハッピーに変える。</t>
+          <t>投稿を、満足に変える。</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -3803,11 +3803,11 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E135" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" ht="19" customHeight="1">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>バズを、笑顔に変える。</t>
+          <t>バズを、喜びに変える。</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E139" s="8" t="n">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>バズを、喜びに変える。</t>
+          <t>バズを、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -3918,11 +3918,11 @@
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E140" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>バズを、ハッピーに変える。</t>
+          <t>バズを、満足に変える。</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -3941,11 +3941,11 @@
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E141" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>拡散を、笑顔に変える。</t>
+          <t>拡散を、喜びに変える。</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E145" s="8" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>拡散を、喜びに変える。</t>
+          <t>拡散を、ハッピーに変える。</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
@@ -4056,11 +4056,11 @@
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E146" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" ht="19" customHeight="1">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>拡散を、ハッピーに変える。</t>
+          <t>拡散を、満足に変える。</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -4079,11 +4079,11 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E147" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>お客様の、笑顔まで。</t>
+          <t>お客様の、喜びまで。</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E151" s="13" t="n">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>お客様の、喜びまで。</t>
+          <t>お客様の、満足まで。</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E152" s="13" t="n">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>お客様の、満足まで。</t>
+          <t>お客様の、豊かさまで。</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
@@ -4217,11 +4217,11 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E153" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" ht="19" customHeight="1">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>つくり手の、笑顔まで。</t>
+          <t>つくり手の、喜びまで。</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E157" s="13" t="n">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>つくり手の、喜びまで。</t>
+          <t>つくり手の、満足まで。</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E158" s="13" t="n">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>つくり手の、満足まで。</t>
+          <t>つくり手の、豊かさまで。</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E159" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160" ht="19" customHeight="1">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>買う人の、笑顔まで。</t>
+          <t>買う人の、喜びまで。</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E163" s="13" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>買う人の、喜びまで。</t>
+          <t>買う人の、満足まで。</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E164" s="13" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>買う人の、満足まで。</t>
+          <t>買う人の、豊かさまで。</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr">
@@ -4493,11 +4493,11 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E165" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" ht="19" customHeight="1">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>売る人の、笑顔まで。</t>
+          <t>売る人の、喜びまで。</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E169" s="13" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>売る人の、喜びまで。</t>
+          <t>売る人の、満足まで。</t>
         </is>
       </c>
       <c r="C170" s="11" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E170" s="13" t="n">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>売る人の、満足まで。</t>
+          <t>売る人の、豊かさまで。</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E171" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172" ht="19" customHeight="1">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>ファンの、笑顔まで。</t>
+          <t>ファンの、喜びまで。</t>
         </is>
       </c>
       <c r="C175" s="11" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E175" s="13" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>ファンの、喜びまで。</t>
+          <t>ファンの、満足まで。</t>
         </is>
       </c>
       <c r="C176" s="11" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E176" s="13" t="n">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>ファンの、満足まで。</t>
+          <t>ファンの、豊かさまで。</t>
         </is>
       </c>
       <c r="C177" s="11" t="inlineStr">
@@ -4769,11 +4769,11 @@
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E177" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" ht="19" customHeight="1">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>みんなの、笑顔まで。</t>
+          <t>みんなの、喜びまで。</t>
         </is>
       </c>
       <c r="C181" s="11" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E181" s="13" t="n">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>みんなの、喜びまで。</t>
+          <t>みんなの、満足まで。</t>
         </is>
       </c>
       <c r="C182" s="11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E182" s="13" t="n">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>みんなの、満足まで。</t>
+          <t>みんなの、豊かさまで。</t>
         </is>
       </c>
       <c r="C183" s="11" t="inlineStr">
@@ -4907,11 +4907,11 @@
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E183" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184" ht="19" customHeight="1">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>買った人の、笑顔まで。</t>
+          <t>買った人の、喜びまで。</t>
         </is>
       </c>
       <c r="C187" s="11" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E187" s="13" t="n">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>買った人の、喜びまで。</t>
+          <t>買った人の、満足まで。</t>
         </is>
       </c>
       <c r="C188" s="11" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E188" s="13" t="n">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>買った人の、満足まで。</t>
+          <t>買った人の、豊かさまで。</t>
         </is>
       </c>
       <c r="C189" s="11" t="inlineStr">
@@ -5045,11 +5045,11 @@
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E189" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" ht="19" customHeight="1">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>店の、笑顔まで。</t>
+          <t>店の、喜びまで。</t>
         </is>
       </c>
       <c r="C193" s="11" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E193" s="13" t="n">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>店の、喜びまで。</t>
+          <t>店の、満足まで。</t>
         </is>
       </c>
       <c r="C194" s="11" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E194" s="13" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>店の、満足まで。</t>
+          <t>店の、豊かさまで。</t>
         </is>
       </c>
       <c r="C195" s="11" t="inlineStr">
@@ -5183,11 +5183,11 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E195" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" ht="19" customHeight="1">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>街の、笑顔まで。</t>
+          <t>街の、喜びまで。</t>
         </is>
       </c>
       <c r="C199" s="11" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E199" s="13" t="n">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>街の、喜びまで。</t>
+          <t>街の、満足まで。</t>
         </is>
       </c>
       <c r="C200" s="11" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E200" s="13" t="n">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>街の、満足まで。</t>
+          <t>街の、豊かさまで。</t>
         </is>
       </c>
       <c r="C201" s="11" t="inlineStr">
@@ -5321,11 +5321,11 @@
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E201" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202" ht="19" customHeight="1">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>つくる人の、笑顔まで。</t>
+          <t>つくる人の、喜びまで。</t>
         </is>
       </c>
       <c r="C205" s="11" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E205" s="13" t="n">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>つくる人の、喜びまで。</t>
+          <t>つくる人の、満足まで。</t>
         </is>
       </c>
       <c r="C206" s="11" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E206" s="13" t="n">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>つくる人の、満足まで。</t>
+          <t>つくる人の、豊かさまで。</t>
         </is>
       </c>
       <c r="C207" s="11" t="inlineStr">
@@ -5459,11 +5459,11 @@
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E207" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208" ht="19" customHeight="1">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>売り手の、笑顔まで。</t>
+          <t>売り手の、喜びまで。</t>
         </is>
       </c>
       <c r="C211" s="11" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E211" s="13" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>売り手の、喜びまで。</t>
+          <t>売り手の、満足まで。</t>
         </is>
       </c>
       <c r="C212" s="11" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E212" s="13" t="n">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>売り手の、満足まで。</t>
+          <t>売り手の、豊かさまで。</t>
         </is>
       </c>
       <c r="C213" s="11" t="inlineStr">
@@ -5597,11 +5597,11 @@
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E213" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214" ht="19" customHeight="1">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>働く人の、笑顔まで。</t>
+          <t>働く人の、喜びまで。</t>
         </is>
       </c>
       <c r="C217" s="11" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E217" s="13" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>働く人の、喜びまで。</t>
+          <t>働く人の、満足まで。</t>
         </is>
       </c>
       <c r="C218" s="11" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E218" s="13" t="n">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>働く人の、満足まで。</t>
+          <t>働く人の、豊かさまで。</t>
         </is>
       </c>
       <c r="C219" s="11" t="inlineStr">
@@ -5735,11 +5735,11 @@
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E219" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220" ht="19" customHeight="1">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="B223" s="15" t="inlineStr">
         <is>
-          <t>その先に、笑顔を。</t>
+          <t>その先に、喜びを。</t>
         </is>
       </c>
       <c r="C223" s="16" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="D223" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E223" s="18" t="n">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B224" s="15" t="inlineStr">
         <is>
-          <t>その先に、喜びを。</t>
+          <t>その先に、よろこびを。</t>
         </is>
       </c>
       <c r="C224" s="16" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D224" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>よろこび</t>
         </is>
       </c>
       <c r="E224" s="18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225" ht="19" customHeight="1">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B225" s="15" t="inlineStr">
         <is>
-          <t>その先に、よろこびを。</t>
+          <t>その先に、ときめきを。</t>
         </is>
       </c>
       <c r="C225" s="16" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="D225" s="17" t="inlineStr">
         <is>
-          <t>よろこび</t>
+          <t>ときめき</t>
         </is>
       </c>
       <c r="E225" s="18" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B226" s="15" t="inlineStr">
         <is>
-          <t>その先に、ときめきを。</t>
+          <t>その先に、満足を。</t>
         </is>
       </c>
       <c r="C226" s="16" t="inlineStr">
@@ -5896,11 +5896,11 @@
       </c>
       <c r="D226" s="17" t="inlineStr">
         <is>
-          <t>ときめき</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E226" s="18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" ht="19" customHeight="1">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="B227" s="15" t="inlineStr">
         <is>
-          <t>その先に、満足を。</t>
+          <t>その先に、豊かさを。</t>
         </is>
       </c>
       <c r="C227" s="16" t="inlineStr">
@@ -5919,11 +5919,11 @@
       </c>
       <c r="D227" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E227" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228" ht="19" customHeight="1">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B228" s="15" t="inlineStr">
         <is>
-          <t>その先に、豊かさを。</t>
+          <t>その先に、感動を。</t>
         </is>
       </c>
       <c r="C228" s="16" t="inlineStr">
@@ -5942,11 +5942,11 @@
       </c>
       <c r="D228" s="17" t="inlineStr">
         <is>
-          <t>豊かさ</t>
+          <t>感動</t>
         </is>
       </c>
       <c r="E228" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" ht="19" customHeight="1">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="B229" s="15" t="inlineStr">
         <is>
-          <t>その先に、感動を。</t>
+          <t>その先に、うれしさを。</t>
         </is>
       </c>
       <c r="C229" s="16" t="inlineStr">
@@ -5965,11 +5965,11 @@
       </c>
       <c r="D229" s="17" t="inlineStr">
         <is>
-          <t>感動</t>
+          <t>うれしさ</t>
         </is>
       </c>
       <c r="E229" s="18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="230" ht="19" customHeight="1">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B230" s="15" t="inlineStr">
         <is>
-          <t>その先に、うれしさを。</t>
+          <t>その先に、ぬくもりを。</t>
         </is>
       </c>
       <c r="C230" s="16" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="D230" s="17" t="inlineStr">
         <is>
-          <t>うれしさ</t>
+          <t>ぬくもり</t>
         </is>
       </c>
       <c r="E230" s="18" t="n">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B231" s="15" t="inlineStr">
         <is>
-          <t>その先に、ぬくもりを。</t>
+          <t>その先に、ゆとりを。</t>
         </is>
       </c>
       <c r="C231" s="16" t="inlineStr">
@@ -6011,11 +6011,11 @@
       </c>
       <c r="D231" s="17" t="inlineStr">
         <is>
-          <t>ぬくもり</t>
+          <t>ゆとり</t>
         </is>
       </c>
       <c r="E231" s="18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232" ht="19" customHeight="1">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="B232" s="15" t="inlineStr">
         <is>
-          <t>その先に、ゆとりを。</t>
+          <t>その先に、安心を。</t>
         </is>
       </c>
       <c r="C232" s="16" t="inlineStr">
@@ -6034,11 +6034,11 @@
       </c>
       <c r="D232" s="17" t="inlineStr">
         <is>
-          <t>ゆとり</t>
+          <t>安心</t>
         </is>
       </c>
       <c r="E232" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" ht="19" customHeight="1">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B233" s="15" t="inlineStr">
         <is>
-          <t>その先に、安心を。</t>
+          <t>その先に、ハッピーを。</t>
         </is>
       </c>
       <c r="C233" s="16" t="inlineStr">
@@ -6057,11 +6057,11 @@
       </c>
       <c r="D233" s="17" t="inlineStr">
         <is>
-          <t>安心</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E233" s="18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234" ht="19" customHeight="1">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B234" s="15" t="inlineStr">
         <is>
-          <t>その先に、ハッピーを。</t>
+          <t>その先に、わくわくを。</t>
         </is>
       </c>
       <c r="C234" s="16" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D234" s="17" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>わくわく</t>
         </is>
       </c>
       <c r="E234" s="18" t="n">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B271" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、つくる。</t>
+          <t>喜びを、つくる。</t>
         </is>
       </c>
       <c r="C271" s="21" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D271" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E271" s="23" t="n">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="B272" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、届ける。</t>
+          <t>喜びを、届ける。</t>
         </is>
       </c>
       <c r="C272" s="21" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="D272" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E272" s="23" t="n">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="B273" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、生む。</t>
+          <t>喜びを、生む。</t>
         </is>
       </c>
       <c r="C273" s="21" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D273" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E273" s="23" t="n">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="B274" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、設計する。</t>
+          <t>喜びを、設計する。</t>
         </is>
       </c>
       <c r="C274" s="21" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="D274" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E274" s="23" t="n">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="B275" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、デザインする。</t>
+          <t>喜びを、デザインする。</t>
         </is>
       </c>
       <c r="C275" s="21" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D275" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E275" s="23" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="B276" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、増やす。</t>
+          <t>喜びを、増やす。</t>
         </is>
       </c>
       <c r="C276" s="21" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D276" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E276" s="23" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="B277" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、広げる。</t>
+          <t>喜びを、広げる。</t>
         </is>
       </c>
       <c r="C277" s="21" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="D277" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E277" s="23" t="n">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="B278" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、運ぶ。</t>
+          <t>喜びを、運ぶ。</t>
         </is>
       </c>
       <c r="C278" s="21" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="D278" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E278" s="23" t="n">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="B279" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、灯す。</t>
+          <t>喜びを、灯す。</t>
         </is>
       </c>
       <c r="C279" s="21" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="D279" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E279" s="23" t="n">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B280" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、育てる。</t>
+          <t>喜びを、育てる。</t>
         </is>
       </c>
       <c r="C280" s="21" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="D280" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E280" s="23" t="n">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B281" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、残す。</t>
+          <t>喜びを、残す。</t>
         </is>
       </c>
       <c r="C281" s="21" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="D281" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E281" s="23" t="n">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="B282" s="20" t="inlineStr">
         <is>
-          <t>笑顔を、つなぐ。</t>
+          <t>喜びを、つなぐ。</t>
         </is>
       </c>
       <c r="C282" s="21" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="D282" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E282" s="23" t="n">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="B283" s="20" t="inlineStr">
         <is>
-          <t>喜びを、つくる。</t>
+          <t>満足を、つくる。</t>
         </is>
       </c>
       <c r="C283" s="21" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="D283" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E283" s="23" t="n">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="B284" s="20" t="inlineStr">
         <is>
-          <t>喜びを、届ける。</t>
+          <t>満足を、届ける。</t>
         </is>
       </c>
       <c r="C284" s="21" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="D284" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E284" s="23" t="n">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="B285" s="20" t="inlineStr">
         <is>
-          <t>喜びを、生む。</t>
+          <t>満足を、生む。</t>
         </is>
       </c>
       <c r="C285" s="21" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D285" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E285" s="23" t="n">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B286" s="20" t="inlineStr">
         <is>
-          <t>喜びを、設計する。</t>
+          <t>満足を、設計する。</t>
         </is>
       </c>
       <c r="C286" s="21" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D286" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E286" s="23" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="B287" s="20" t="inlineStr">
         <is>
-          <t>喜びを、デザインする。</t>
+          <t>満足を、デザインする。</t>
         </is>
       </c>
       <c r="C287" s="21" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="D287" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E287" s="23" t="n">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="B288" s="20" t="inlineStr">
         <is>
-          <t>喜びを、増やす。</t>
+          <t>満足を、増やす。</t>
         </is>
       </c>
       <c r="C288" s="21" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D288" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E288" s="23" t="n">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="B289" s="20" t="inlineStr">
         <is>
-          <t>喜びを、広げる。</t>
+          <t>満足を、広げる。</t>
         </is>
       </c>
       <c r="C289" s="21" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="D289" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E289" s="23" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="B290" s="20" t="inlineStr">
         <is>
-          <t>喜びを、運ぶ。</t>
+          <t>満足を、運ぶ。</t>
         </is>
       </c>
       <c r="C290" s="21" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D290" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E290" s="23" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="B291" s="20" t="inlineStr">
         <is>
-          <t>喜びを、灯す。</t>
+          <t>満足を、灯す。</t>
         </is>
       </c>
       <c r="C291" s="21" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D291" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E291" s="23" t="n">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="B292" s="20" t="inlineStr">
         <is>
-          <t>喜びを、育てる。</t>
+          <t>満足を、育てる。</t>
         </is>
       </c>
       <c r="C292" s="21" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="D292" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E292" s="23" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="B293" s="20" t="inlineStr">
         <is>
-          <t>喜びを、残す。</t>
+          <t>満足を、残す。</t>
         </is>
       </c>
       <c r="C293" s="21" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="D293" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E293" s="23" t="n">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="B294" s="20" t="inlineStr">
         <is>
-          <t>喜びを、つなぐ。</t>
+          <t>満足を、つなぐ。</t>
         </is>
       </c>
       <c r="C294" s="21" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="D294" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E294" s="23" t="n">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>笑顔が、売上になる。</t>
+          <t>喜びが、売上になる。</t>
         </is>
       </c>
       <c r="C319" s="26" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="D319" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E319" s="28" t="n">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>笑顔が、めぐる。</t>
+          <t>喜びが、めぐる。</t>
         </is>
       </c>
       <c r="C320" s="26" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D320" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E320" s="28" t="n">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>笑顔が、広がる。</t>
+          <t>喜びが、広がる。</t>
         </is>
       </c>
       <c r="C321" s="26" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D321" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E321" s="28" t="n">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>笑顔が、増えていく。</t>
+          <t>喜びが、増えていく。</t>
         </is>
       </c>
       <c r="C322" s="26" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="D322" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E322" s="28" t="n">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>笑顔が、ファンをつくる。</t>
+          <t>喜びが、ファンをつくる。</t>
         </is>
       </c>
       <c r="C323" s="26" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D323" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E323" s="28" t="n">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>笑顔が、次の売上を呼ぶ。</t>
+          <t>喜びが、次の売上を呼ぶ。</t>
         </is>
       </c>
       <c r="C324" s="26" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D324" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E324" s="28" t="n">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>笑顔が、人を集める。</t>
+          <t>喜びが、人を集める。</t>
         </is>
       </c>
       <c r="C325" s="26" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="D325" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E325" s="28" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>笑顔が、連鎖する。</t>
+          <t>喜びが、連鎖する。</t>
         </is>
       </c>
       <c r="C326" s="26" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="D326" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E326" s="28" t="n">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>喜びが、売上になる。</t>
+          <t>満足が、売上になる。</t>
         </is>
       </c>
       <c r="C327" s="26" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D327" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E327" s="28" t="n">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>喜びが、めぐる。</t>
+          <t>満足が、めぐる。</t>
         </is>
       </c>
       <c r="C328" s="26" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D328" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E328" s="28" t="n">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>喜びが、広がる。</t>
+          <t>満足が、広がる。</t>
         </is>
       </c>
       <c r="C329" s="26" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="D329" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E329" s="28" t="n">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>喜びが、増えていく。</t>
+          <t>満足が、増えていく。</t>
         </is>
       </c>
       <c r="C330" s="26" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="D330" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E330" s="28" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>喜びが、ファンをつくる。</t>
+          <t>満足が、ファンをつくる。</t>
         </is>
       </c>
       <c r="C331" s="26" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D331" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E331" s="28" t="n">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>喜びが、次の売上を呼ぶ。</t>
+          <t>満足が、次の売上を呼ぶ。</t>
         </is>
       </c>
       <c r="C332" s="26" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D332" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E332" s="28" t="n">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>喜びが、人を集める。</t>
+          <t>満足が、人を集める。</t>
         </is>
       </c>
       <c r="C333" s="26" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="D333" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E333" s="28" t="n">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>喜びが、連鎖する。</t>
+          <t>満足が、連鎖する。</t>
         </is>
       </c>
       <c r="C334" s="26" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D334" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E334" s="28" t="n">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="B371" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、つくり手。</t>
+          <t>喜びの、つくり手。</t>
         </is>
       </c>
       <c r="C371" s="31" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D371" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E371" s="33" t="n">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="B372" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、設計図。</t>
+          <t>喜びの、設計図。</t>
         </is>
       </c>
       <c r="C372" s="31" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="D372" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E372" s="33" t="n">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B373" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、循環。</t>
+          <t>喜びの、循環。</t>
         </is>
       </c>
       <c r="C373" s="31" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="D373" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E373" s="33" t="n">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="B374" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、つくり方。</t>
+          <t>喜びの、つくり方。</t>
         </is>
       </c>
       <c r="C374" s="31" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="D374" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E374" s="33" t="n">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="B375" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、はじまり。</t>
+          <t>喜びの、はじまり。</t>
         </is>
       </c>
       <c r="C375" s="31" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="D375" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E375" s="33" t="n">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="B376" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、輪。</t>
+          <t>喜びの、輪。</t>
         </is>
       </c>
       <c r="C376" s="31" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D376" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E376" s="33" t="n">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B377" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、連鎖。</t>
+          <t>喜びの、連鎖。</t>
         </is>
       </c>
       <c r="C377" s="31" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="D377" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E377" s="33" t="n">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="B378" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、専門家。</t>
+          <t>喜びの、専門家。</t>
         </is>
       </c>
       <c r="C378" s="31" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="D378" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E378" s="33" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="B379" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、デザイン。</t>
+          <t>喜びの、デザイン。</t>
         </is>
       </c>
       <c r="C379" s="31" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D379" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E379" s="33" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="B380" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、種。</t>
+          <t>喜びの、種。</t>
         </is>
       </c>
       <c r="C380" s="31" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="D380" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E380" s="33" t="n">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="B381" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、かたち。</t>
+          <t>喜びの、かたち。</t>
         </is>
       </c>
       <c r="C381" s="31" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D381" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E381" s="33" t="n">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B382" s="30" t="inlineStr">
         <is>
-          <t>笑顔の、場所。</t>
+          <t>喜びの、場所。</t>
         </is>
       </c>
       <c r="C382" s="31" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="D382" s="32" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E382" s="33" t="n">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="B383" s="30" t="inlineStr">
         <is>
-          <t>喜びの、つくり手。</t>
+          <t>満足の、つくり手。</t>
         </is>
       </c>
       <c r="C383" s="31" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="D383" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E383" s="33" t="n">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="B384" s="30" t="inlineStr">
         <is>
-          <t>喜びの、設計図。</t>
+          <t>満足の、設計図。</t>
         </is>
       </c>
       <c r="C384" s="31" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="D384" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E384" s="33" t="n">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="B385" s="30" t="inlineStr">
         <is>
-          <t>喜びの、循環。</t>
+          <t>満足の、循環。</t>
         </is>
       </c>
       <c r="C385" s="31" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="D385" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E385" s="33" t="n">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="B386" s="30" t="inlineStr">
         <is>
-          <t>喜びの、つくり方。</t>
+          <t>満足の、つくり方。</t>
         </is>
       </c>
       <c r="C386" s="31" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D386" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E386" s="33" t="n">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="B387" s="30" t="inlineStr">
         <is>
-          <t>喜びの、はじまり。</t>
+          <t>満足の、はじまり。</t>
         </is>
       </c>
       <c r="C387" s="31" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="D387" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E387" s="33" t="n">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B388" s="30" t="inlineStr">
         <is>
-          <t>喜びの、輪。</t>
+          <t>満足の、輪。</t>
         </is>
       </c>
       <c r="C388" s="31" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D388" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E388" s="33" t="n">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="B389" s="30" t="inlineStr">
         <is>
-          <t>喜びの、連鎖。</t>
+          <t>満足の、連鎖。</t>
         </is>
       </c>
       <c r="C389" s="31" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="D389" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E389" s="33" t="n">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="B390" s="30" t="inlineStr">
         <is>
-          <t>喜びの、専門家。</t>
+          <t>満足の、専門家。</t>
         </is>
       </c>
       <c r="C390" s="31" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="D390" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E390" s="33" t="n">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="B391" s="30" t="inlineStr">
         <is>
-          <t>喜びの、デザイン。</t>
+          <t>満足の、デザイン。</t>
         </is>
       </c>
       <c r="C391" s="31" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D391" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E391" s="33" t="n">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B392" s="30" t="inlineStr">
         <is>
-          <t>喜びの、種。</t>
+          <t>満足の、種。</t>
         </is>
       </c>
       <c r="C392" s="31" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="D392" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E392" s="33" t="n">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="B393" s="30" t="inlineStr">
         <is>
-          <t>喜びの、かたち。</t>
+          <t>満足の、かたち。</t>
         </is>
       </c>
       <c r="C393" s="31" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="D393" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E393" s="33" t="n">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="B394" s="30" t="inlineStr">
         <is>
-          <t>喜びの、場所。</t>
+          <t>満足の、場所。</t>
         </is>
       </c>
       <c r="C394" s="31" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="D394" s="32" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E394" s="33" t="n">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B398" s="35" t="inlineStr">
         <is>
-          <t>売れた数だけ、笑顔も。</t>
+          <t>売れた数だけ、喜びも。</t>
         </is>
       </c>
       <c r="C398" s="36" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="D398" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E398" s="38" t="n">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="B399" s="35" t="inlineStr">
         <is>
-          <t>売れた数だけ、喜びも。</t>
+          <t>売れた数だけ、満足も。</t>
         </is>
       </c>
       <c r="C399" s="36" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="D399" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E399" s="38" t="n">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="B403" s="35" t="inlineStr">
         <is>
-          <t>売れた分だけ、笑顔も。</t>
+          <t>売れた分だけ、喜びも。</t>
         </is>
       </c>
       <c r="C403" s="36" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="D403" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E403" s="38" t="n">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="B404" s="35" t="inlineStr">
         <is>
-          <t>売れた分だけ、喜びも。</t>
+          <t>売れた分だけ、満足も。</t>
         </is>
       </c>
       <c r="C404" s="36" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="D404" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E404" s="38" t="n">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="B408" s="40" t="inlineStr">
         <is>
-          <t>お客様を、笑顔にする会社。</t>
+          <t>お客様を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C408" s="41" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="D408" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E408" s="43" t="n">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="B409" s="40" t="inlineStr">
         <is>
-          <t>お客様を、喜びにする会社。</t>
+          <t>お客様を、満足にする会社。</t>
         </is>
       </c>
       <c r="C409" s="41" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="D409" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E409" s="43" t="n">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="B413" s="40" t="inlineStr">
         <is>
-          <t>つくり手を、笑顔にする会社。</t>
+          <t>つくり手を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C413" s="41" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="D413" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E413" s="43" t="n">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="B414" s="40" t="inlineStr">
         <is>
-          <t>つくり手を、喜びにする会社。</t>
+          <t>つくり手を、満足にする会社。</t>
         </is>
       </c>
       <c r="C414" s="41" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="D414" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E414" s="43" t="n">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B418" s="40" t="inlineStr">
         <is>
-          <t>買う人を、笑顔にする会社。</t>
+          <t>買う人を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C418" s="41" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D418" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E418" s="43" t="n">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="B419" s="40" t="inlineStr">
         <is>
-          <t>買う人を、喜びにする会社。</t>
+          <t>買う人を、満足にする会社。</t>
         </is>
       </c>
       <c r="C419" s="41" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="D419" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E419" s="43" t="n">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="B423" s="40" t="inlineStr">
         <is>
-          <t>売る人を、笑顔にする会社。</t>
+          <t>売る人を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C423" s="41" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="D423" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E423" s="43" t="n">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B424" s="40" t="inlineStr">
         <is>
-          <t>売る人を、喜びにする会社。</t>
+          <t>売る人を、満足にする会社。</t>
         </is>
       </c>
       <c r="C424" s="41" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="D424" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E424" s="43" t="n">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="B428" s="40" t="inlineStr">
         <is>
-          <t>ファンを、笑顔にする会社。</t>
+          <t>ファンを、喜びにする会社。</t>
         </is>
       </c>
       <c r="C428" s="41" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="D428" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E428" s="43" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="B429" s="40" t="inlineStr">
         <is>
-          <t>ファンを、喜びにする会社。</t>
+          <t>ファンを、満足にする会社。</t>
         </is>
       </c>
       <c r="C429" s="41" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="D429" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E429" s="43" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="B433" s="40" t="inlineStr">
         <is>
-          <t>みんなを、笑顔にする会社。</t>
+          <t>みんなを、喜びにする会社。</t>
         </is>
       </c>
       <c r="C433" s="41" t="inlineStr">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="D433" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E433" s="43" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="B434" s="40" t="inlineStr">
         <is>
-          <t>みんなを、喜びにする会社。</t>
+          <t>みんなを、満足にする会社。</t>
         </is>
       </c>
       <c r="C434" s="41" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="D434" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E434" s="43" t="n">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="B438" s="40" t="inlineStr">
         <is>
-          <t>買った人を、笑顔にする会社。</t>
+          <t>買った人を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C438" s="41" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="D438" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E438" s="43" t="n">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="B439" s="40" t="inlineStr">
         <is>
-          <t>買った人を、喜びにする会社。</t>
+          <t>買った人を、満足にする会社。</t>
         </is>
       </c>
       <c r="C439" s="41" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="D439" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E439" s="43" t="n">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="B443" s="40" t="inlineStr">
         <is>
-          <t>店を、笑顔にする会社。</t>
+          <t>店を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C443" s="41" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="D443" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E443" s="43" t="n">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="B444" s="40" t="inlineStr">
         <is>
-          <t>店を、喜びにする会社。</t>
+          <t>店を、満足にする会社。</t>
         </is>
       </c>
       <c r="C444" s="41" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="D444" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E444" s="43" t="n">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B448" s="40" t="inlineStr">
         <is>
-          <t>街を、笑顔にする会社。</t>
+          <t>街を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C448" s="41" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="D448" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E448" s="43" t="n">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="B449" s="40" t="inlineStr">
         <is>
-          <t>街を、喜びにする会社。</t>
+          <t>街を、満足にする会社。</t>
         </is>
       </c>
       <c r="C449" s="41" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="D449" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E449" s="43" t="n">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="B453" s="40" t="inlineStr">
         <is>
-          <t>つくる人を、笑顔にする会社。</t>
+          <t>つくる人を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C453" s="41" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="D453" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E453" s="43" t="n">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="B454" s="40" t="inlineStr">
         <is>
-          <t>つくる人を、喜びにする会社。</t>
+          <t>つくる人を、満足にする会社。</t>
         </is>
       </c>
       <c r="C454" s="41" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="D454" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E454" s="43" t="n">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="B458" s="40" t="inlineStr">
         <is>
-          <t>売り手を、笑顔にする会社。</t>
+          <t>売り手を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C458" s="41" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="D458" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E458" s="43" t="n">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="B459" s="40" t="inlineStr">
         <is>
-          <t>売り手を、喜びにする会社。</t>
+          <t>売り手を、満足にする会社。</t>
         </is>
       </c>
       <c r="C459" s="41" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="D459" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E459" s="43" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B463" s="40" t="inlineStr">
         <is>
-          <t>働く人を、笑顔にする会社。</t>
+          <t>働く人を、喜びにする会社。</t>
         </is>
       </c>
       <c r="C463" s="41" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="D463" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E463" s="43" t="n">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="B464" s="40" t="inlineStr">
         <is>
-          <t>働く人を、喜びにする会社。</t>
+          <t>働く人を、満足にする会社。</t>
         </is>
       </c>
       <c r="C464" s="41" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="D464" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E464" s="43" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B501" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、つくる。</t>
+          <t>喜びまで、つくる。</t>
         </is>
       </c>
       <c r="C501" s="21" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="D501" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E501" s="23" t="n">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="B502" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、届ける。</t>
+          <t>喜びまで、届ける。</t>
         </is>
       </c>
       <c r="C502" s="21" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="D502" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E502" s="23" t="n">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="B503" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、生む。</t>
+          <t>喜びまで、生む。</t>
         </is>
       </c>
       <c r="C503" s="21" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="D503" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E503" s="23" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="B504" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、設計する。</t>
+          <t>喜びまで、設計する。</t>
         </is>
       </c>
       <c r="C504" s="21" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="D504" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E504" s="23" t="n">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="B505" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、デザインする。</t>
+          <t>喜びまで、デザインする。</t>
         </is>
       </c>
       <c r="C505" s="21" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="D505" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E505" s="23" t="n">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="B506" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、増やす。</t>
+          <t>喜びまで、増やす。</t>
         </is>
       </c>
       <c r="C506" s="21" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D506" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E506" s="23" t="n">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="B507" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、広げる。</t>
+          <t>喜びまで、広げる。</t>
         </is>
       </c>
       <c r="C507" s="21" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="D507" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E507" s="23" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="B508" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、運ぶ。</t>
+          <t>喜びまで、運ぶ。</t>
         </is>
       </c>
       <c r="C508" s="21" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="D508" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E508" s="23" t="n">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="B509" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、灯す。</t>
+          <t>喜びまで、灯す。</t>
         </is>
       </c>
       <c r="C509" s="21" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="D509" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E509" s="23" t="n">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="B510" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、育てる。</t>
+          <t>喜びまで、育てる。</t>
         </is>
       </c>
       <c r="C510" s="21" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="D510" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E510" s="23" t="n">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="B511" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、残す。</t>
+          <t>喜びまで、残す。</t>
         </is>
       </c>
       <c r="C511" s="21" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="D511" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E511" s="23" t="n">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="B512" s="20" t="inlineStr">
         <is>
-          <t>笑顔まで、つなぐ。</t>
+          <t>喜びまで、つなぐ。</t>
         </is>
       </c>
       <c r="C512" s="21" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="D512" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E512" s="23" t="n">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="B513" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、つくる。</t>
+          <t>満足まで、つくる。</t>
         </is>
       </c>
       <c r="C513" s="21" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="D513" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E513" s="23" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B514" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、届ける。</t>
+          <t>満足まで、届ける。</t>
         </is>
       </c>
       <c r="C514" s="21" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="D514" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E514" s="23" t="n">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="B515" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、生む。</t>
+          <t>満足まで、生む。</t>
         </is>
       </c>
       <c r="C515" s="21" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="D515" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E515" s="23" t="n">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="B516" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、設計する。</t>
+          <t>満足まで、設計する。</t>
         </is>
       </c>
       <c r="C516" s="21" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="D516" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E516" s="23" t="n">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="B517" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、デザインする。</t>
+          <t>満足まで、デザインする。</t>
         </is>
       </c>
       <c r="C517" s="21" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="D517" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E517" s="23" t="n">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="B518" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、増やす。</t>
+          <t>満足まで、増やす。</t>
         </is>
       </c>
       <c r="C518" s="21" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="D518" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E518" s="23" t="n">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="B519" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、広げる。</t>
+          <t>満足まで、広げる。</t>
         </is>
       </c>
       <c r="C519" s="21" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="D519" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E519" s="23" t="n">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="B520" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、運ぶ。</t>
+          <t>満足まで、運ぶ。</t>
         </is>
       </c>
       <c r="C520" s="21" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="D520" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E520" s="23" t="n">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="B521" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、灯す。</t>
+          <t>満足まで、灯す。</t>
         </is>
       </c>
       <c r="C521" s="21" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D521" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E521" s="23" t="n">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="B522" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、育てる。</t>
+          <t>満足まで、育てる。</t>
         </is>
       </c>
       <c r="C522" s="21" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="D522" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E522" s="23" t="n">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="B523" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、残す。</t>
+          <t>満足まで、残す。</t>
         </is>
       </c>
       <c r="C523" s="21" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="D523" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E523" s="23" t="n">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="B524" s="20" t="inlineStr">
         <is>
-          <t>喜びまで、つなぐ。</t>
+          <t>満足まで、つなぐ。</t>
         </is>
       </c>
       <c r="C524" s="21" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="D524" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E524" s="23" t="n">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="B528" s="15" t="inlineStr">
         <is>
-          <t>売上の先に、笑顔を。</t>
+          <t>売上の先に、喜びを。</t>
         </is>
       </c>
       <c r="C528" s="16" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="D528" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E528" s="18" t="n">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="B529" s="15" t="inlineStr">
         <is>
-          <t>売上の先に、喜びを。</t>
+          <t>売上の先に、満足を。</t>
         </is>
       </c>
       <c r="C529" s="16" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="D529" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E529" s="18" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B530" s="15" t="inlineStr">
         <is>
-          <t>売上の先に、満足を。</t>
+          <t>売上の先に、豊かさを。</t>
         </is>
       </c>
       <c r="C530" s="16" t="inlineStr">
@@ -12888,11 +12888,11 @@
       </c>
       <c r="D530" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E530" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="531" ht="19" customHeight="1">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="B534" s="15" t="inlineStr">
         <is>
-          <t>数字の先に、笑顔を。</t>
+          <t>数字の先に、喜びを。</t>
         </is>
       </c>
       <c r="C534" s="16" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="D534" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E534" s="18" t="n">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="B535" s="15" t="inlineStr">
         <is>
-          <t>数字の先に、喜びを。</t>
+          <t>数字の先に、満足を。</t>
         </is>
       </c>
       <c r="C535" s="16" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="D535" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E535" s="18" t="n">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="B536" s="15" t="inlineStr">
         <is>
-          <t>数字の先に、満足を。</t>
+          <t>数字の先に、豊かさを。</t>
         </is>
       </c>
       <c r="C536" s="16" t="inlineStr">
@@ -13026,11 +13026,11 @@
       </c>
       <c r="D536" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E536" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="537" ht="19" customHeight="1">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="B540" s="15" t="inlineStr">
         <is>
-          <t>「売れた」の先に、笑顔を。</t>
+          <t>「売れた」の先に、喜びを。</t>
         </is>
       </c>
       <c r="C540" s="16" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="D540" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E540" s="18" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B541" s="15" t="inlineStr">
         <is>
-          <t>「売れた」の先に、喜びを。</t>
+          <t>「売れた」の先に、満足を。</t>
         </is>
       </c>
       <c r="C541" s="16" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="D541" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E541" s="18" t="n">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="B542" s="15" t="inlineStr">
         <is>
-          <t>「売れた」の先に、満足を。</t>
+          <t>「売れた」の先に、豊かさを。</t>
         </is>
       </c>
       <c r="C542" s="16" t="inlineStr">
@@ -13164,11 +13164,11 @@
       </c>
       <c r="D542" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E542" s="18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="543" ht="19" customHeight="1">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="B546" s="15" t="inlineStr">
         <is>
-          <t>フォロワーの先に、笑顔を。</t>
+          <t>フォロワーの先に、喜びを。</t>
         </is>
       </c>
       <c r="C546" s="16" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="D546" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E546" s="18" t="n">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="B547" s="15" t="inlineStr">
         <is>
-          <t>フォロワーの先に、喜びを。</t>
+          <t>フォロワーの先に、満足を。</t>
         </is>
       </c>
       <c r="C547" s="16" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="D547" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E547" s="18" t="n">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="B548" s="15" t="inlineStr">
         <is>
-          <t>フォロワーの先に、満足を。</t>
+          <t>フォロワーの先に、豊かさを。</t>
         </is>
       </c>
       <c r="C548" s="16" t="inlineStr">
@@ -13302,11 +13302,11 @@
       </c>
       <c r="D548" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E548" s="18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="549" ht="19" customHeight="1">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="B552" s="15" t="inlineStr">
         <is>
-          <t>投稿の先に、笑顔を。</t>
+          <t>投稿の先に、喜びを。</t>
         </is>
       </c>
       <c r="C552" s="16" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="D552" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E552" s="18" t="n">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="B553" s="15" t="inlineStr">
         <is>
-          <t>投稿の先に、喜びを。</t>
+          <t>投稿の先に、満足を。</t>
         </is>
       </c>
       <c r="C553" s="16" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="D553" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E553" s="18" t="n">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="B554" s="15" t="inlineStr">
         <is>
-          <t>投稿の先に、満足を。</t>
+          <t>投稿の先に、豊かさを。</t>
         </is>
       </c>
       <c r="C554" s="16" t="inlineStr">
@@ -13440,11 +13440,11 @@
       </c>
       <c r="D554" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E554" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="555" ht="19" customHeight="1">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="B558" s="15" t="inlineStr">
         <is>
-          <t>拡散の先に、笑顔を。</t>
+          <t>拡散の先に、喜びを。</t>
         </is>
       </c>
       <c r="C558" s="16" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="D558" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E558" s="18" t="n">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B559" s="15" t="inlineStr">
         <is>
-          <t>拡散の先に、喜びを。</t>
+          <t>拡散の先に、満足を。</t>
         </is>
       </c>
       <c r="C559" s="16" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="D559" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E559" s="18" t="n">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="B560" s="15" t="inlineStr">
         <is>
-          <t>拡散の先に、満足を。</t>
+          <t>拡散の先に、豊かさを。</t>
         </is>
       </c>
       <c r="C560" s="16" t="inlineStr">
@@ -13578,11 +13578,11 @@
       </c>
       <c r="D560" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E560" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="561" ht="19" customHeight="1">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="B564" s="15" t="inlineStr">
         <is>
-          <t>売上の、その先の笑顔まで。</t>
+          <t>売上の、その先の喜びまで。</t>
         </is>
       </c>
       <c r="C564" s="16" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="D564" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E564" s="18" t="n">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="B565" s="15" t="inlineStr">
         <is>
-          <t>売上の、その先の喜びまで。</t>
+          <t>売上の、その先の満足まで。</t>
         </is>
       </c>
       <c r="C565" s="16" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="D565" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E565" s="18" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="B566" s="15" t="inlineStr">
         <is>
-          <t>売上の、その先の満足まで。</t>
+          <t>売上の、その先の豊かさまで。</t>
         </is>
       </c>
       <c r="C566" s="16" t="inlineStr">
@@ -13716,11 +13716,11 @@
       </c>
       <c r="D566" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E566" s="18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="567" ht="19" customHeight="1">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B570" s="15" t="inlineStr">
         <is>
-          <t>数字の、その先の笑顔まで。</t>
+          <t>数字の、その先の喜びまで。</t>
         </is>
       </c>
       <c r="C570" s="16" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="D570" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E570" s="18" t="n">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="B571" s="15" t="inlineStr">
         <is>
-          <t>数字の、その先の喜びまで。</t>
+          <t>数字の、その先の満足まで。</t>
         </is>
       </c>
       <c r="C571" s="16" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="D571" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E571" s="18" t="n">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="B572" s="15" t="inlineStr">
         <is>
-          <t>数字の、その先の満足まで。</t>
+          <t>数字の、その先の豊かさまで。</t>
         </is>
       </c>
       <c r="C572" s="16" t="inlineStr">
@@ -13854,11 +13854,11 @@
       </c>
       <c r="D572" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E572" s="18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="573" ht="19" customHeight="1">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B576" s="15" t="inlineStr">
         <is>
-          <t>「売れた」の、その先の笑顔まで。</t>
+          <t>「売れた」の、その先の喜びまで。</t>
         </is>
       </c>
       <c r="C576" s="16" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="D576" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E576" s="18" t="n">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="B577" s="15" t="inlineStr">
         <is>
-          <t>「売れた」の、その先の喜びまで。</t>
+          <t>「売れた」の、その先の満足まで。</t>
         </is>
       </c>
       <c r="C577" s="16" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="D577" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E577" s="18" t="n">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="B578" s="15" t="inlineStr">
         <is>
-          <t>「売れた」の、その先の満足まで。</t>
+          <t>「売れた」の、その先の豊かさまで。</t>
         </is>
       </c>
       <c r="C578" s="16" t="inlineStr">
@@ -13992,11 +13992,11 @@
       </c>
       <c r="D578" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E578" s="18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="579" ht="19" customHeight="1">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="B582" s="15" t="inlineStr">
         <is>
-          <t>フォロワーの、その先の笑顔まで。</t>
+          <t>フォロワーの、その先の喜びまで。</t>
         </is>
       </c>
       <c r="C582" s="16" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="D582" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E582" s="18" t="n">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="B583" s="15" t="inlineStr">
         <is>
-          <t>フォロワーの、その先の喜びまで。</t>
+          <t>フォロワーの、その先の満足まで。</t>
         </is>
       </c>
       <c r="C583" s="16" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="D583" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E583" s="18" t="n">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B584" s="15" t="inlineStr">
         <is>
-          <t>フォロワーの、その先の満足まで。</t>
+          <t>フォロワーの、その先の豊かさまで。</t>
         </is>
       </c>
       <c r="C584" s="16" t="inlineStr">
@@ -14130,11 +14130,11 @@
       </c>
       <c r="D584" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E584" s="18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="585" ht="19" customHeight="1">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="B588" s="15" t="inlineStr">
         <is>
-          <t>投稿の、その先の笑顔まで。</t>
+          <t>投稿の、その先の喜びまで。</t>
         </is>
       </c>
       <c r="C588" s="16" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="D588" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E588" s="18" t="n">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="B589" s="15" t="inlineStr">
         <is>
-          <t>投稿の、その先の喜びまで。</t>
+          <t>投稿の、その先の満足まで。</t>
         </is>
       </c>
       <c r="C589" s="16" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="D589" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E589" s="18" t="n">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="B590" s="15" t="inlineStr">
         <is>
-          <t>投稿の、その先の満足まで。</t>
+          <t>投稿の、その先の豊かさまで。</t>
         </is>
       </c>
       <c r="C590" s="16" t="inlineStr">
@@ -14268,11 +14268,11 @@
       </c>
       <c r="D590" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E590" s="18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="591" ht="19" customHeight="1">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="B594" s="15" t="inlineStr">
         <is>
-          <t>拡散の、その先の笑顔まで。</t>
+          <t>拡散の、その先の喜びまで。</t>
         </is>
       </c>
       <c r="C594" s="16" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="D594" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E594" s="18" t="n">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="B595" s="15" t="inlineStr">
         <is>
-          <t>拡散の、その先の喜びまで。</t>
+          <t>拡散の、その先の満足まで。</t>
         </is>
       </c>
       <c r="C595" s="16" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="D595" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E595" s="18" t="n">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="B596" s="15" t="inlineStr">
         <is>
-          <t>拡散の、その先の満足まで。</t>
+          <t>拡散の、その先の豊かさまで。</t>
         </is>
       </c>
       <c r="C596" s="16" t="inlineStr">
@@ -14406,11 +14406,11 @@
       </c>
       <c r="D596" s="17" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E596" s="18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="597" ht="19" customHeight="1">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B600" s="45" t="inlineStr">
         <is>
-          <t>笑顔も、売上も。</t>
+          <t>喜びも、売上も。</t>
         </is>
       </c>
       <c r="C600" s="46" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="D600" s="47" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E600" s="48" t="n">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="B601" s="45" t="inlineStr">
         <is>
-          <t>喜びも、売上も。</t>
+          <t>よろこびも、売上も。</t>
         </is>
       </c>
       <c r="C601" s="46" t="inlineStr">
@@ -14521,11 +14521,11 @@
       </c>
       <c r="D601" s="47" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>よろこび</t>
         </is>
       </c>
       <c r="E601" s="48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="602" ht="19" customHeight="1">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="B602" s="45" t="inlineStr">
         <is>
-          <t>よろこびも、売上も。</t>
+          <t>ときめきも、売上も。</t>
         </is>
       </c>
       <c r="C602" s="46" t="inlineStr">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="D602" s="47" t="inlineStr">
         <is>
-          <t>よろこび</t>
+          <t>ときめき</t>
         </is>
       </c>
       <c r="E602" s="48" t="n">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="B603" s="45" t="inlineStr">
         <is>
-          <t>ときめきも、売上も。</t>
+          <t>満足も、売上も。</t>
         </is>
       </c>
       <c r="C603" s="46" t="inlineStr">
@@ -14567,11 +14567,11 @@
       </c>
       <c r="D603" s="47" t="inlineStr">
         <is>
-          <t>ときめき</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E603" s="48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="604" ht="19" customHeight="1">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B604" s="45" t="inlineStr">
         <is>
-          <t>満足も、売上も。</t>
+          <t>豊かさも、売上も。</t>
         </is>
       </c>
       <c r="C604" s="46" t="inlineStr">
@@ -14590,11 +14590,11 @@
       </c>
       <c r="D604" s="47" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E604" s="48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="605" ht="19" customHeight="1">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="B605" s="45" t="inlineStr">
         <is>
-          <t>豊かさも、売上も。</t>
+          <t>感動も、売上も。</t>
         </is>
       </c>
       <c r="C605" s="46" t="inlineStr">
@@ -14613,11 +14613,11 @@
       </c>
       <c r="D605" s="47" t="inlineStr">
         <is>
-          <t>豊かさ</t>
+          <t>感動</t>
         </is>
       </c>
       <c r="E605" s="48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="606" ht="19" customHeight="1">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="B606" s="45" t="inlineStr">
         <is>
-          <t>感動も、売上も。</t>
+          <t>うれしさも、売上も。</t>
         </is>
       </c>
       <c r="C606" s="46" t="inlineStr">
@@ -14636,11 +14636,11 @@
       </c>
       <c r="D606" s="47" t="inlineStr">
         <is>
-          <t>感動</t>
+          <t>うれしさ</t>
         </is>
       </c>
       <c r="E606" s="48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="607" ht="19" customHeight="1">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B607" s="45" t="inlineStr">
         <is>
-          <t>うれしさも、売上も。</t>
+          <t>ぬくもりも、売上も。</t>
         </is>
       </c>
       <c r="C607" s="46" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="D607" s="47" t="inlineStr">
         <is>
-          <t>うれしさ</t>
+          <t>ぬくもり</t>
         </is>
       </c>
       <c r="E607" s="48" t="n">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B608" s="45" t="inlineStr">
         <is>
-          <t>ぬくもりも、売上も。</t>
+          <t>ゆとりも、売上も。</t>
         </is>
       </c>
       <c r="C608" s="46" t="inlineStr">
@@ -14682,11 +14682,11 @@
       </c>
       <c r="D608" s="47" t="inlineStr">
         <is>
-          <t>ぬくもり</t>
+          <t>ゆとり</t>
         </is>
       </c>
       <c r="E608" s="48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="609" ht="19" customHeight="1">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="B609" s="45" t="inlineStr">
         <is>
-          <t>ゆとりも、売上も。</t>
+          <t>安心も、売上も。</t>
         </is>
       </c>
       <c r="C609" s="46" t="inlineStr">
@@ -14705,11 +14705,11 @@
       </c>
       <c r="D609" s="47" t="inlineStr">
         <is>
-          <t>ゆとり</t>
+          <t>安心</t>
         </is>
       </c>
       <c r="E609" s="48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="610" ht="19" customHeight="1">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="B610" s="45" t="inlineStr">
         <is>
-          <t>安心も、売上も。</t>
+          <t>ハッピーも、売上も。</t>
         </is>
       </c>
       <c r="C610" s="46" t="inlineStr">
@@ -14728,11 +14728,11 @@
       </c>
       <c r="D610" s="47" t="inlineStr">
         <is>
-          <t>安心</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E610" s="48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="611" ht="19" customHeight="1">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="B611" s="45" t="inlineStr">
         <is>
-          <t>ハッピーも、売上も。</t>
+          <t>わくわくも、売上も。</t>
         </is>
       </c>
       <c r="C611" s="46" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="D611" s="47" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>わくわく</t>
         </is>
       </c>
       <c r="E611" s="48" t="n">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="B615" s="50" t="inlineStr">
         <is>
-          <t>笑顔から、はじめる。</t>
+          <t>喜びから、はじめる。</t>
         </is>
       </c>
       <c r="C615" s="51" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="D615" s="52" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E615" s="53" t="n">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="B616" s="50" t="inlineStr">
         <is>
-          <t>喜びから、はじめる。</t>
+          <t>満足から、はじめる。</t>
         </is>
       </c>
       <c r="C616" s="51" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="D616" s="52" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E616" s="53" t="n">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="B620" s="45" t="inlineStr">
         <is>
-          <t>笑顔を、売上に変える。</t>
+          <t>喜びを、売上に変える。</t>
         </is>
       </c>
       <c r="C620" s="46" t="inlineStr">
@@ -14958,7 +14958,7 @@
       </c>
       <c r="D620" s="47" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E620" s="48" t="n">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="B621" s="45" t="inlineStr">
         <is>
-          <t>喜びを、売上に変える。</t>
+          <t>満足を、売上に変える。</t>
         </is>
       </c>
       <c r="C621" s="46" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="D621" s="47" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E621" s="48" t="n">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="B625" s="10" t="inlineStr">
         <is>
-          <t>お客様の、笑顔のために。</t>
+          <t>お客様の、喜びのために。</t>
         </is>
       </c>
       <c r="C625" s="11" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="D625" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E625" s="13" t="n">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="B626" s="10" t="inlineStr">
         <is>
-          <t>お客様の、喜びのために。</t>
+          <t>お客様の、満足のために。</t>
         </is>
       </c>
       <c r="C626" s="11" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="D626" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E626" s="13" t="n">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="B630" s="10" t="inlineStr">
         <is>
-          <t>つくり手の、笑顔のために。</t>
+          <t>つくり手の、喜びのために。</t>
         </is>
       </c>
       <c r="C630" s="11" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="D630" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E630" s="13" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="B631" s="10" t="inlineStr">
         <is>
-          <t>つくり手の、喜びのために。</t>
+          <t>つくり手の、満足のために。</t>
         </is>
       </c>
       <c r="C631" s="11" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="D631" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E631" s="13" t="n">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="B635" s="10" t="inlineStr">
         <is>
-          <t>買う人の、笑顔のために。</t>
+          <t>買う人の、喜びのために。</t>
         </is>
       </c>
       <c r="C635" s="11" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="D635" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E635" s="13" t="n">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="B636" s="10" t="inlineStr">
         <is>
-          <t>買う人の、喜びのために。</t>
+          <t>買う人の、満足のために。</t>
         </is>
       </c>
       <c r="C636" s="11" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="D636" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E636" s="13" t="n">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="B640" s="10" t="inlineStr">
         <is>
-          <t>売る人の、笑顔のために。</t>
+          <t>売る人の、喜びのために。</t>
         </is>
       </c>
       <c r="C640" s="11" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="D640" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E640" s="13" t="n">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="B641" s="10" t="inlineStr">
         <is>
-          <t>売る人の、喜びのために。</t>
+          <t>売る人の、満足のために。</t>
         </is>
       </c>
       <c r="C641" s="11" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="D641" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E641" s="13" t="n">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="B645" s="10" t="inlineStr">
         <is>
-          <t>ファンの、笑顔のために。</t>
+          <t>ファンの、喜びのために。</t>
         </is>
       </c>
       <c r="C645" s="11" t="inlineStr">
@@ -15533,7 +15533,7 @@
       </c>
       <c r="D645" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E645" s="13" t="n">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="B646" s="10" t="inlineStr">
         <is>
-          <t>ファンの、喜びのために。</t>
+          <t>ファンの、満足のために。</t>
         </is>
       </c>
       <c r="C646" s="11" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="D646" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E646" s="13" t="n">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="B650" s="10" t="inlineStr">
         <is>
-          <t>みんなの、笑顔のために。</t>
+          <t>みんなの、喜びのために。</t>
         </is>
       </c>
       <c r="C650" s="11" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="D650" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E650" s="13" t="n">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="B651" s="10" t="inlineStr">
         <is>
-          <t>みんなの、喜びのために。</t>
+          <t>みんなの、満足のために。</t>
         </is>
       </c>
       <c r="C651" s="11" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="D651" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E651" s="13" t="n">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="B655" s="10" t="inlineStr">
         <is>
-          <t>買った人の、笑顔のために。</t>
+          <t>買った人の、喜びのために。</t>
         </is>
       </c>
       <c r="C655" s="11" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="D655" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E655" s="13" t="n">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="B656" s="10" t="inlineStr">
         <is>
-          <t>買った人の、喜びのために。</t>
+          <t>買った人の、満足のために。</t>
         </is>
       </c>
       <c r="C656" s="11" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="D656" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E656" s="13" t="n">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="B660" s="10" t="inlineStr">
         <is>
-          <t>店の、笑顔のために。</t>
+          <t>店の、喜びのために。</t>
         </is>
       </c>
       <c r="C660" s="11" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="D660" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E660" s="13" t="n">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B661" s="10" t="inlineStr">
         <is>
-          <t>店の、喜びのために。</t>
+          <t>店の、満足のために。</t>
         </is>
       </c>
       <c r="C661" s="11" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="D661" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E661" s="13" t="n">
@@ -15983,7 +15983,7 @@
       </c>
       <c r="B665" s="10" t="inlineStr">
         <is>
-          <t>街の、笑顔のために。</t>
+          <t>街の、喜びのために。</t>
         </is>
       </c>
       <c r="C665" s="11" t="inlineStr">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="D665" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E665" s="13" t="n">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="B666" s="10" t="inlineStr">
         <is>
-          <t>街の、喜びのために。</t>
+          <t>街の、満足のために。</t>
         </is>
       </c>
       <c r="C666" s="11" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="D666" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E666" s="13" t="n">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="B670" s="10" t="inlineStr">
         <is>
-          <t>つくる人の、笑顔のために。</t>
+          <t>つくる人の、喜びのために。</t>
         </is>
       </c>
       <c r="C670" s="11" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="D670" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E670" s="13" t="n">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="B671" s="10" t="inlineStr">
         <is>
-          <t>つくる人の、喜びのために。</t>
+          <t>つくる人の、満足のために。</t>
         </is>
       </c>
       <c r="C671" s="11" t="inlineStr">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="D671" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E671" s="13" t="n">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="B675" s="10" t="inlineStr">
         <is>
-          <t>売り手の、笑顔のために。</t>
+          <t>売り手の、喜びのために。</t>
         </is>
       </c>
       <c r="C675" s="11" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="D675" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E675" s="13" t="n">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="B676" s="10" t="inlineStr">
         <is>
-          <t>売り手の、喜びのために。</t>
+          <t>売り手の、満足のために。</t>
         </is>
       </c>
       <c r="C676" s="11" t="inlineStr">
@@ -16246,7 +16246,7 @@
       </c>
       <c r="D676" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E676" s="13" t="n">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B680" s="10" t="inlineStr">
         <is>
-          <t>働く人の、笑顔のために。</t>
+          <t>働く人の、喜びのために。</t>
         </is>
       </c>
       <c r="C680" s="11" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="D680" s="12" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E680" s="13" t="n">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="B681" s="10" t="inlineStr">
         <is>
-          <t>働く人の、喜びのために。</t>
+          <t>働く人の、満足のために。</t>
         </is>
       </c>
       <c r="C681" s="11" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="D681" s="12" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E681" s="13" t="n">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="B685" s="15" t="inlineStr">
         <is>
-          <t>フォロワーから、笑顔まで。</t>
+          <t>フォロワーから、喜びまで。</t>
         </is>
       </c>
       <c r="C685" s="16" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="D685" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E685" s="18" t="n">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="B686" s="15" t="inlineStr">
         <is>
-          <t>フォロワーから、喜びまで。</t>
+          <t>フォロワーから、満足まで。</t>
         </is>
       </c>
       <c r="C686" s="16" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="D686" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E686" s="18" t="n">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="B690" s="15" t="inlineStr">
         <is>
-          <t>お客様から、笑顔まで。</t>
+          <t>お客様から、喜びまで。</t>
         </is>
       </c>
       <c r="C690" s="16" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="D690" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E690" s="18" t="n">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="B691" s="15" t="inlineStr">
         <is>
-          <t>お客様から、喜びまで。</t>
+          <t>お客様から、満足まで。</t>
         </is>
       </c>
       <c r="C691" s="16" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="D691" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E691" s="18" t="n">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="B695" s="15" t="inlineStr">
         <is>
-          <t>ファンから、笑顔まで。</t>
+          <t>ファンから、喜びまで。</t>
         </is>
       </c>
       <c r="C695" s="16" t="inlineStr">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="D695" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E695" s="18" t="n">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="B696" s="15" t="inlineStr">
         <is>
-          <t>ファンから、喜びまで。</t>
+          <t>ファンから、満足まで。</t>
         </is>
       </c>
       <c r="C696" s="16" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D696" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E696" s="18" t="n">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="B700" s="15" t="inlineStr">
         <is>
-          <t>商品から、笑顔まで。</t>
+          <t>商品から、喜びまで。</t>
         </is>
       </c>
       <c r="C700" s="16" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="D700" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E700" s="18" t="n">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="B701" s="15" t="inlineStr">
         <is>
-          <t>商品から、喜びまで。</t>
+          <t>商品から、満足まで。</t>
         </is>
       </c>
       <c r="C701" s="16" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="D701" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E701" s="18" t="n">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="B705" s="15" t="inlineStr">
         <is>
-          <t>売上から、笑顔まで。</t>
+          <t>売上から、喜びまで。</t>
         </is>
       </c>
       <c r="C705" s="16" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="D705" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E705" s="18" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B706" s="15" t="inlineStr">
         <is>
-          <t>売上から、喜びまで。</t>
+          <t>売上から、満足まで。</t>
         </is>
       </c>
       <c r="C706" s="16" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="D706" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E706" s="18" t="n">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="B710" s="15" t="inlineStr">
         <is>
-          <t>数字から、笑顔まで。</t>
+          <t>数字から、喜びまで。</t>
         </is>
       </c>
       <c r="C710" s="16" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="D710" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E710" s="18" t="n">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="B711" s="15" t="inlineStr">
         <is>
-          <t>数字から、喜びまで。</t>
+          <t>数字から、満足まで。</t>
         </is>
       </c>
       <c r="C711" s="16" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="D711" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E711" s="18" t="n">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="B715" s="15" t="inlineStr">
         <is>
-          <t>「好き」から、笑顔まで。</t>
+          <t>「好き」から、喜びまで。</t>
         </is>
       </c>
       <c r="C715" s="16" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="D715" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E715" s="18" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="B716" s="15" t="inlineStr">
         <is>
-          <t>「好き」から、喜びまで。</t>
+          <t>「好き」から、満足まで。</t>
         </is>
       </c>
       <c r="C716" s="16" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="D716" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E716" s="18" t="n">
@@ -17248,7 +17248,7 @@
       </c>
       <c r="B720" s="15" t="inlineStr">
         <is>
-          <t>出会いから、笑顔まで。</t>
+          <t>出会いから、喜びまで。</t>
         </is>
       </c>
       <c r="C720" s="16" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="D720" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E720" s="18" t="n">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="B721" s="15" t="inlineStr">
         <is>
-          <t>出会いから、喜びまで。</t>
+          <t>出会いから、満足まで。</t>
         </is>
       </c>
       <c r="C721" s="16" t="inlineStr">
@@ -17281,7 +17281,7 @@
       </c>
       <c r="D721" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E721" s="18" t="n">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="B725" s="15" t="inlineStr">
         <is>
-          <t>「いいね」から、笑顔まで。</t>
+          <t>「いいね」から、喜びまで。</t>
         </is>
       </c>
       <c r="C725" s="16" t="inlineStr">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="D725" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E725" s="18" t="n">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="B726" s="15" t="inlineStr">
         <is>
-          <t>「いいね」から、喜びまで。</t>
+          <t>「いいね」から、満足まで。</t>
         </is>
       </c>
       <c r="C726" s="16" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="D726" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E726" s="18" t="n">
@@ -17478,7 +17478,7 @@
       </c>
       <c r="B730" s="15" t="inlineStr">
         <is>
-          <t>投稿から、笑顔まで。</t>
+          <t>投稿から、喜びまで。</t>
         </is>
       </c>
       <c r="C730" s="16" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="D730" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E730" s="18" t="n">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="B731" s="15" t="inlineStr">
         <is>
-          <t>投稿から、喜びまで。</t>
+          <t>投稿から、満足まで。</t>
         </is>
       </c>
       <c r="C731" s="16" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="D731" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E731" s="18" t="n">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="B735" s="15" t="inlineStr">
         <is>
-          <t>バズから、笑顔まで。</t>
+          <t>バズから、喜びまで。</t>
         </is>
       </c>
       <c r="C735" s="16" t="inlineStr">
@@ -17603,7 +17603,7 @@
       </c>
       <c r="D735" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E735" s="18" t="n">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="B736" s="15" t="inlineStr">
         <is>
-          <t>バズから、喜びまで。</t>
+          <t>バズから、満足まで。</t>
         </is>
       </c>
       <c r="C736" s="16" t="inlineStr">
@@ -17626,7 +17626,7 @@
       </c>
       <c r="D736" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E736" s="18" t="n">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="B740" s="15" t="inlineStr">
         <is>
-          <t>拡散から、笑顔まで。</t>
+          <t>拡散から、喜びまで。</t>
         </is>
       </c>
       <c r="C740" s="16" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="D740" s="17" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E740" s="18" t="n">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="B741" s="15" t="inlineStr">
         <is>
-          <t>拡散から、喜びまで。</t>
+          <t>拡散から、満足まで。</t>
         </is>
       </c>
       <c r="C741" s="16" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="D741" s="17" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E741" s="18" t="n">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="B745" s="20" t="inlineStr">
         <is>
-          <t>お客様の笑顔を、つくる。</t>
+          <t>お客様の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C745" s="21" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="D745" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E745" s="23" t="n">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="B746" s="20" t="inlineStr">
         <is>
-          <t>お客様の喜びを、つくる。</t>
+          <t>お客様の満足を、つくる。</t>
         </is>
       </c>
       <c r="C746" s="21" t="inlineStr">
@@ -17856,7 +17856,7 @@
       </c>
       <c r="D746" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E746" s="23" t="n">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="B750" s="20" t="inlineStr">
         <is>
-          <t>つくり手の笑顔を、つくる。</t>
+          <t>つくり手の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C750" s="21" t="inlineStr">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="D750" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E750" s="23" t="n">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="B751" s="20" t="inlineStr">
         <is>
-          <t>つくり手の喜びを、つくる。</t>
+          <t>つくり手の満足を、つくる。</t>
         </is>
       </c>
       <c r="C751" s="21" t="inlineStr">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="D751" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E751" s="23" t="n">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="B755" s="20" t="inlineStr">
         <is>
-          <t>買う人の笑顔を、つくる。</t>
+          <t>買う人の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C755" s="21" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="D755" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E755" s="23" t="n">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="B756" s="20" t="inlineStr">
         <is>
-          <t>買う人の喜びを、つくる。</t>
+          <t>買う人の満足を、つくる。</t>
         </is>
       </c>
       <c r="C756" s="21" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="D756" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E756" s="23" t="n">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="B760" s="20" t="inlineStr">
         <is>
-          <t>売る人の笑顔を、つくる。</t>
+          <t>売る人の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C760" s="21" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="D760" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E760" s="23" t="n">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="B761" s="20" t="inlineStr">
         <is>
-          <t>売る人の喜びを、つくる。</t>
+          <t>売る人の満足を、つくる。</t>
         </is>
       </c>
       <c r="C761" s="21" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="D761" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E761" s="23" t="n">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="B765" s="20" t="inlineStr">
         <is>
-          <t>ファンの笑顔を、つくる。</t>
+          <t>ファンの喜びを、つくる。</t>
         </is>
       </c>
       <c r="C765" s="21" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="D765" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E765" s="23" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="B766" s="20" t="inlineStr">
         <is>
-          <t>ファンの喜びを、つくる。</t>
+          <t>ファンの満足を、つくる。</t>
         </is>
       </c>
       <c r="C766" s="21" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="D766" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E766" s="23" t="n">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="B770" s="20" t="inlineStr">
         <is>
-          <t>みんなの笑顔を、つくる。</t>
+          <t>みんなの喜びを、つくる。</t>
         </is>
       </c>
       <c r="C770" s="21" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="D770" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E770" s="23" t="n">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="B771" s="20" t="inlineStr">
         <is>
-          <t>みんなの喜びを、つくる。</t>
+          <t>みんなの満足を、つくる。</t>
         </is>
       </c>
       <c r="C771" s="21" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="D771" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E771" s="23" t="n">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="B775" s="20" t="inlineStr">
         <is>
-          <t>買った人の笑顔を、つくる。</t>
+          <t>買った人の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C775" s="21" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="D775" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E775" s="23" t="n">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="B776" s="20" t="inlineStr">
         <is>
-          <t>買った人の喜びを、つくる。</t>
+          <t>買った人の満足を、つくる。</t>
         </is>
       </c>
       <c r="C776" s="21" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="D776" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E776" s="23" t="n">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="B780" s="20" t="inlineStr">
         <is>
-          <t>店の笑顔を、つくる。</t>
+          <t>店の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C780" s="21" t="inlineStr">
@@ -18638,7 +18638,7 @@
       </c>
       <c r="D780" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E780" s="23" t="n">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="B781" s="20" t="inlineStr">
         <is>
-          <t>店の喜びを、つくる。</t>
+          <t>店の満足を、つくる。</t>
         </is>
       </c>
       <c r="C781" s="21" t="inlineStr">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="D781" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E781" s="23" t="n">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="B785" s="20" t="inlineStr">
         <is>
-          <t>街の笑顔を、つくる。</t>
+          <t>街の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C785" s="21" t="inlineStr">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="D785" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E785" s="23" t="n">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="B786" s="20" t="inlineStr">
         <is>
-          <t>街の喜びを、つくる。</t>
+          <t>街の満足を、つくる。</t>
         </is>
       </c>
       <c r="C786" s="21" t="inlineStr">
@@ -18776,7 +18776,7 @@
       </c>
       <c r="D786" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E786" s="23" t="n">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="B790" s="20" t="inlineStr">
         <is>
-          <t>つくる人の笑顔を、つくる。</t>
+          <t>つくる人の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C790" s="21" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="D790" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E790" s="23" t="n">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="B791" s="20" t="inlineStr">
         <is>
-          <t>つくる人の喜びを、つくる。</t>
+          <t>つくる人の満足を、つくる。</t>
         </is>
       </c>
       <c r="C791" s="21" t="inlineStr">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="D791" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E791" s="23" t="n">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="B795" s="20" t="inlineStr">
         <is>
-          <t>売り手の笑顔を、つくる。</t>
+          <t>売り手の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C795" s="21" t="inlineStr">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="D795" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E795" s="23" t="n">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="B796" s="20" t="inlineStr">
         <is>
-          <t>売り手の喜びを、つくる。</t>
+          <t>売り手の満足を、つくる。</t>
         </is>
       </c>
       <c r="C796" s="21" t="inlineStr">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="D796" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E796" s="23" t="n">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="B800" s="20" t="inlineStr">
         <is>
-          <t>働く人の笑顔を、つくる。</t>
+          <t>働く人の喜びを、つくる。</t>
         </is>
       </c>
       <c r="C800" s="21" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="D800" s="22" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E800" s="23" t="n">
@@ -19111,7 +19111,7 @@
       </c>
       <c r="B801" s="20" t="inlineStr">
         <is>
-          <t>働く人の喜びを、つくる。</t>
+          <t>働く人の満足を、つくる。</t>
         </is>
       </c>
       <c r="C801" s="21" t="inlineStr">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="D801" s="22" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E801" s="23" t="n">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="B805" s="35" t="inlineStr">
         <is>
-          <t>お客様の数だけ、笑顔を。</t>
+          <t>お客様の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C805" s="36" t="inlineStr">
@@ -19213,7 +19213,7 @@
       </c>
       <c r="D805" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E805" s="38" t="n">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="B806" s="35" t="inlineStr">
         <is>
-          <t>お客様の数だけ、喜びを。</t>
+          <t>お客様の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C806" s="36" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="D806" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E806" s="38" t="n">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="B810" s="35" t="inlineStr">
         <is>
-          <t>つくり手の数だけ、笑顔を。</t>
+          <t>つくり手の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C810" s="36" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="D810" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E810" s="38" t="n">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="B811" s="35" t="inlineStr">
         <is>
-          <t>つくり手の数だけ、喜びを。</t>
+          <t>つくり手の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C811" s="36" t="inlineStr">
@@ -19351,7 +19351,7 @@
       </c>
       <c r="D811" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E811" s="38" t="n">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="B815" s="35" t="inlineStr">
         <is>
-          <t>買う人の数だけ、笑顔を。</t>
+          <t>買う人の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C815" s="36" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="D815" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E815" s="38" t="n">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B816" s="35" t="inlineStr">
         <is>
-          <t>買う人の数だけ、喜びを。</t>
+          <t>買う人の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C816" s="36" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="D816" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E816" s="38" t="n">
@@ -19548,7 +19548,7 @@
       </c>
       <c r="B820" s="35" t="inlineStr">
         <is>
-          <t>売る人の数だけ、笑顔を。</t>
+          <t>売る人の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C820" s="36" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="D820" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E820" s="38" t="n">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="B821" s="35" t="inlineStr">
         <is>
-          <t>売る人の数だけ、喜びを。</t>
+          <t>売る人の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C821" s="36" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="D821" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E821" s="38" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="B825" s="35" t="inlineStr">
         <is>
-          <t>ファンの数だけ、笑顔を。</t>
+          <t>ファンの数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C825" s="36" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="D825" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E825" s="38" t="n">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="B826" s="35" t="inlineStr">
         <is>
-          <t>ファンの数だけ、喜びを。</t>
+          <t>ファンの数だけ、満足を。</t>
         </is>
       </c>
       <c r="C826" s="36" t="inlineStr">
@@ -19696,7 +19696,7 @@
       </c>
       <c r="D826" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E826" s="38" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="B830" s="35" t="inlineStr">
         <is>
-          <t>みんなの数だけ、笑顔を。</t>
+          <t>みんなの数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C830" s="36" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="D830" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E830" s="38" t="n">
@@ -19801,7 +19801,7 @@
       </c>
       <c r="B831" s="35" t="inlineStr">
         <is>
-          <t>みんなの数だけ、喜びを。</t>
+          <t>みんなの数だけ、満足を。</t>
         </is>
       </c>
       <c r="C831" s="36" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="D831" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E831" s="38" t="n">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="B835" s="35" t="inlineStr">
         <is>
-          <t>買った人の数だけ、笑顔を。</t>
+          <t>買った人の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C835" s="36" t="inlineStr">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="D835" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E835" s="38" t="n">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="B836" s="35" t="inlineStr">
         <is>
-          <t>買った人の数だけ、喜びを。</t>
+          <t>買った人の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C836" s="36" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="D836" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E836" s="38" t="n">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="B840" s="35" t="inlineStr">
         <is>
-          <t>店の数だけ、笑顔を。</t>
+          <t>店の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C840" s="36" t="inlineStr">
@@ -20018,7 +20018,7 @@
       </c>
       <c r="D840" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E840" s="38" t="n">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="B841" s="35" t="inlineStr">
         <is>
-          <t>店の数だけ、喜びを。</t>
+          <t>店の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C841" s="36" t="inlineStr">
@@ -20041,7 +20041,7 @@
       </c>
       <c r="D841" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E841" s="38" t="n">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="B845" s="35" t="inlineStr">
         <is>
-          <t>街の数だけ、笑顔を。</t>
+          <t>街の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C845" s="36" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="D845" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E845" s="38" t="n">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="B846" s="35" t="inlineStr">
         <is>
-          <t>街の数だけ、喜びを。</t>
+          <t>街の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C846" s="36" t="inlineStr">
@@ -20156,7 +20156,7 @@
       </c>
       <c r="D846" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E846" s="38" t="n">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="B850" s="35" t="inlineStr">
         <is>
-          <t>つくる人の数だけ、笑顔を。</t>
+          <t>つくる人の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C850" s="36" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="D850" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E850" s="38" t="n">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="B851" s="35" t="inlineStr">
         <is>
-          <t>つくる人の数だけ、喜びを。</t>
+          <t>つくる人の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C851" s="36" t="inlineStr">
@@ -20271,7 +20271,7 @@
       </c>
       <c r="D851" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E851" s="38" t="n">
@@ -20353,7 +20353,7 @@
       </c>
       <c r="B855" s="35" t="inlineStr">
         <is>
-          <t>売り手の数だけ、笑顔を。</t>
+          <t>売り手の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C855" s="36" t="inlineStr">
@@ -20363,7 +20363,7 @@
       </c>
       <c r="D855" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E855" s="38" t="n">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="B856" s="35" t="inlineStr">
         <is>
-          <t>売り手の数だけ、喜びを。</t>
+          <t>売り手の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C856" s="36" t="inlineStr">
@@ -20386,7 +20386,7 @@
       </c>
       <c r="D856" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E856" s="38" t="n">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="B860" s="35" t="inlineStr">
         <is>
-          <t>働く人の数だけ、笑顔を。</t>
+          <t>働く人の数だけ、喜びを。</t>
         </is>
       </c>
       <c r="C860" s="36" t="inlineStr">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="D860" s="37" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E860" s="38" t="n">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="B861" s="35" t="inlineStr">
         <is>
-          <t>働く人の数だけ、喜びを。</t>
+          <t>働く人の数だけ、満足を。</t>
         </is>
       </c>
       <c r="C861" s="36" t="inlineStr">
@@ -20501,7 +20501,7 @@
       </c>
       <c r="D861" s="37" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E861" s="38" t="n">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="B865" s="25" t="inlineStr">
         <is>
-          <t>お客様の笑顔が、ふえる。</t>
+          <t>お客様の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C865" s="26" t="inlineStr">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="D865" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E865" s="28" t="n">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="B866" s="25" t="inlineStr">
         <is>
-          <t>お客様の喜びが、ふえる。</t>
+          <t>お客様の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C866" s="26" t="inlineStr">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="D866" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E866" s="28" t="n">
@@ -20698,7 +20698,7 @@
       </c>
       <c r="B870" s="25" t="inlineStr">
         <is>
-          <t>つくり手の笑顔が、ふえる。</t>
+          <t>つくり手の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C870" s="26" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="D870" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E870" s="28" t="n">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="B871" s="25" t="inlineStr">
         <is>
-          <t>つくり手の喜びが、ふえる。</t>
+          <t>つくり手の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C871" s="26" t="inlineStr">
@@ -20731,7 +20731,7 @@
       </c>
       <c r="D871" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E871" s="28" t="n">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="B875" s="25" t="inlineStr">
         <is>
-          <t>買う人の笑顔が、ふえる。</t>
+          <t>買う人の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C875" s="26" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="D875" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E875" s="28" t="n">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="B876" s="25" t="inlineStr">
         <is>
-          <t>買う人の喜びが、ふえる。</t>
+          <t>買う人の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C876" s="26" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="D876" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E876" s="28" t="n">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="B880" s="25" t="inlineStr">
         <is>
-          <t>売る人の笑顔が、ふえる。</t>
+          <t>売る人の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C880" s="26" t="inlineStr">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="D880" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E880" s="28" t="n">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="B881" s="25" t="inlineStr">
         <is>
-          <t>売る人の喜びが、ふえる。</t>
+          <t>売る人の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C881" s="26" t="inlineStr">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="D881" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E881" s="28" t="n">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="B885" s="25" t="inlineStr">
         <is>
-          <t>ファンの笑顔が、ふえる。</t>
+          <t>ファンの喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C885" s="26" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="D885" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E885" s="28" t="n">
@@ -21066,7 +21066,7 @@
       </c>
       <c r="B886" s="25" t="inlineStr">
         <is>
-          <t>ファンの喜びが、ふえる。</t>
+          <t>ファンの満足が、ふえる。</t>
         </is>
       </c>
       <c r="C886" s="26" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="D886" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E886" s="28" t="n">
@@ -21158,7 +21158,7 @@
       </c>
       <c r="B890" s="25" t="inlineStr">
         <is>
-          <t>みんなの笑顔が、ふえる。</t>
+          <t>みんなの喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C890" s="26" t="inlineStr">
@@ -21168,7 +21168,7 @@
       </c>
       <c r="D890" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E890" s="28" t="n">
@@ -21181,7 +21181,7 @@
       </c>
       <c r="B891" s="25" t="inlineStr">
         <is>
-          <t>みんなの喜びが、ふえる。</t>
+          <t>みんなの満足が、ふえる。</t>
         </is>
       </c>
       <c r="C891" s="26" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="D891" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E891" s="28" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="B895" s="25" t="inlineStr">
         <is>
-          <t>買った人の笑顔が、ふえる。</t>
+          <t>買った人の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C895" s="26" t="inlineStr">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="D895" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E895" s="28" t="n">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="B896" s="25" t="inlineStr">
         <is>
-          <t>買った人の喜びが、ふえる。</t>
+          <t>買った人の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C896" s="26" t="inlineStr">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="D896" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E896" s="28" t="n">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="B900" s="25" t="inlineStr">
         <is>
-          <t>店の笑顔が、ふえる。</t>
+          <t>店の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C900" s="26" t="inlineStr">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="D900" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E900" s="28" t="n">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="B901" s="25" t="inlineStr">
         <is>
-          <t>店の喜びが、ふえる。</t>
+          <t>店の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C901" s="26" t="inlineStr">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="D901" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E901" s="28" t="n">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="B905" s="25" t="inlineStr">
         <is>
-          <t>街の笑顔が、ふえる。</t>
+          <t>街の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C905" s="26" t="inlineStr">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="D905" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E905" s="28" t="n">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="B906" s="25" t="inlineStr">
         <is>
-          <t>街の喜びが、ふえる。</t>
+          <t>街の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C906" s="26" t="inlineStr">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="D906" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E906" s="28" t="n">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="B910" s="25" t="inlineStr">
         <is>
-          <t>つくる人の笑顔が、ふえる。</t>
+          <t>つくる人の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C910" s="26" t="inlineStr">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="D910" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E910" s="28" t="n">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="B911" s="25" t="inlineStr">
         <is>
-          <t>つくる人の喜びが、ふえる。</t>
+          <t>つくる人の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C911" s="26" t="inlineStr">
@@ -21651,7 +21651,7 @@
       </c>
       <c r="D911" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E911" s="28" t="n">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="B915" s="25" t="inlineStr">
         <is>
-          <t>売り手の笑顔が、ふえる。</t>
+          <t>売り手の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C915" s="26" t="inlineStr">
@@ -21743,7 +21743,7 @@
       </c>
       <c r="D915" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E915" s="28" t="n">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="B916" s="25" t="inlineStr">
         <is>
-          <t>売り手の喜びが、ふえる。</t>
+          <t>売り手の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C916" s="26" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="D916" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E916" s="28" t="n">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="B920" s="25" t="inlineStr">
         <is>
-          <t>働く人の笑顔が、ふえる。</t>
+          <t>働く人の喜びが、ふえる。</t>
         </is>
       </c>
       <c r="C920" s="26" t="inlineStr">
@@ -21858,7 +21858,7 @@
       </c>
       <c r="D920" s="27" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E920" s="28" t="n">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="B921" s="25" t="inlineStr">
         <is>
-          <t>働く人の喜びが、ふえる。</t>
+          <t>働く人の満足が、ふえる。</t>
         </is>
       </c>
       <c r="C921" s="26" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="D921" s="27" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E921" s="28" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B925" s="55" t="inlineStr">
         <is>
-          <t>売り手も、買い手も、笑顔に。</t>
+          <t>売り手も、買い手も、喜びに。</t>
         </is>
       </c>
       <c r="C925" s="56" t="inlineStr">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="D925" s="57" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E925" s="58" t="n">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="B926" s="55" t="inlineStr">
         <is>
-          <t>売り手も、買い手も、喜びに。</t>
+          <t>売り手も、買い手も、満足に。</t>
         </is>
       </c>
       <c r="C926" s="56" t="inlineStr">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="D926" s="57" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E926" s="58" t="n">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="B930" s="55" t="inlineStr">
         <is>
-          <t>つくる人も、買う人も、笑顔に。</t>
+          <t>つくる人も、買う人も、喜びに。</t>
         </is>
       </c>
       <c r="C930" s="56" t="inlineStr">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="D930" s="57" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E930" s="58" t="n">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="B931" s="55" t="inlineStr">
         <is>
-          <t>つくる人も、買う人も、喜びに。</t>
+          <t>つくる人も、買う人も、満足に。</t>
         </is>
       </c>
       <c r="C931" s="56" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="D931" s="57" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E931" s="58" t="n">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="B935" s="55" t="inlineStr">
         <is>
-          <t>売る人も、買う人も、笑顔に。</t>
+          <t>売る人も、買う人も、喜びに。</t>
         </is>
       </c>
       <c r="C935" s="56" t="inlineStr">
@@ -22203,7 +22203,7 @@
       </c>
       <c r="D935" s="57" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E935" s="58" t="n">
@@ -22216,7 +22216,7 @@
       </c>
       <c r="B936" s="55" t="inlineStr">
         <is>
-          <t>売る人も、買う人も、喜びに。</t>
+          <t>売る人も、買う人も、満足に。</t>
         </is>
       </c>
       <c r="C936" s="56" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="D936" s="57" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E936" s="58" t="n">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="B940" s="55" t="inlineStr">
         <is>
-          <t>お客様も、つくり手も、笑顔に。</t>
+          <t>お客様も、つくり手も、喜びに。</t>
         </is>
       </c>
       <c r="C940" s="56" t="inlineStr">
@@ -22318,7 +22318,7 @@
       </c>
       <c r="D940" s="57" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E940" s="58" t="n">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="B941" s="55" t="inlineStr">
         <is>
-          <t>お客様も、つくり手も、喜びに。</t>
+          <t>お客様も、つくり手も、満足に。</t>
         </is>
       </c>
       <c r="C941" s="56" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="D941" s="57" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E941" s="58" t="n">
@@ -22561,7 +22561,7 @@
       </c>
       <c r="B951" s="45" t="inlineStr">
         <is>
-          <t>笑顔は、売上から。</t>
+          <t>喜びは、売上から。</t>
         </is>
       </c>
       <c r="C951" s="46" t="inlineStr">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="D951" s="47" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E951" s="48" t="n">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="B952" s="40" t="inlineStr">
         <is>
-          <t>笑顔に、こだわる。</t>
+          <t>喜びに、こだわる。</t>
         </is>
       </c>
       <c r="C952" s="41" t="inlineStr">
@@ -22594,7 +22594,7 @@
       </c>
       <c r="D952" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E952" s="43" t="n">
@@ -22607,7 +22607,7 @@
       </c>
       <c r="B953" s="45" t="inlineStr">
         <is>
-          <t>その笑顔を、売上に。</t>
+          <t>その喜びを、売上に。</t>
         </is>
       </c>
       <c r="C953" s="46" t="inlineStr">
@@ -22617,7 +22617,7 @@
       </c>
       <c r="D953" s="47" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E953" s="48" t="n">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="B954" s="45" t="inlineStr">
         <is>
-          <t>喜びは、売上から。</t>
+          <t>満足は、売上から。</t>
         </is>
       </c>
       <c r="C954" s="46" t="inlineStr">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="D954" s="47" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E954" s="48" t="n">
@@ -22653,7 +22653,7 @@
       </c>
       <c r="B955" s="40" t="inlineStr">
         <is>
-          <t>喜びに、こだわる。</t>
+          <t>満足に、こだわる。</t>
         </is>
       </c>
       <c r="C955" s="41" t="inlineStr">
@@ -22663,7 +22663,7 @@
       </c>
       <c r="D955" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E955" s="43" t="n">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="B956" s="45" t="inlineStr">
         <is>
-          <t>その喜びを、売上に。</t>
+          <t>その満足を、売上に。</t>
         </is>
       </c>
       <c r="C956" s="46" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="D956" s="47" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E956" s="48" t="n">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="B963" s="60" t="inlineStr">
         <is>
-          <t>笑顔を、あなたに。</t>
+          <t>喜びを、あなたに。</t>
         </is>
       </c>
       <c r="C963" s="61" t="inlineStr">
@@ -22847,7 +22847,7 @@
       </c>
       <c r="D963" s="62" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E963" s="63" t="n">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="B964" s="60" t="inlineStr">
         <is>
-          <t>笑顔を、もっと。</t>
+          <t>喜びを、もっと。</t>
         </is>
       </c>
       <c r="C964" s="61" t="inlineStr">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="D964" s="62" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E964" s="63" t="n">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="B965" s="60" t="inlineStr">
         <is>
-          <t>喜びを、あなたに。</t>
+          <t>よろこびを、あなたに。</t>
         </is>
       </c>
       <c r="C965" s="61" t="inlineStr">
@@ -22893,11 +22893,11 @@
       </c>
       <c r="D965" s="62" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>よろこび</t>
         </is>
       </c>
       <c r="E965" s="63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="966" ht="19" customHeight="1">
@@ -22906,7 +22906,7 @@
       </c>
       <c r="B966" s="60" t="inlineStr">
         <is>
-          <t>喜びを、もっと。</t>
+          <t>よろこびを、もっと。</t>
         </is>
       </c>
       <c r="C966" s="61" t="inlineStr">
@@ -22916,11 +22916,11 @@
       </c>
       <c r="D966" s="62" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>よろこび</t>
         </is>
       </c>
       <c r="E966" s="63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="967" ht="19" customHeight="1">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="B967" s="60" t="inlineStr">
         <is>
-          <t>よろこびを、あなたに。</t>
+          <t>ときめきを、あなたに。</t>
         </is>
       </c>
       <c r="C967" s="61" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="D967" s="62" t="inlineStr">
         <is>
-          <t>よろこび</t>
+          <t>ときめき</t>
         </is>
       </c>
       <c r="E967" s="63" t="n">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="B968" s="60" t="inlineStr">
         <is>
-          <t>よろこびを、もっと。</t>
+          <t>ときめきを、もっと。</t>
         </is>
       </c>
       <c r="C968" s="61" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="D968" s="62" t="inlineStr">
         <is>
-          <t>よろこび</t>
+          <t>ときめき</t>
         </is>
       </c>
       <c r="E968" s="63" t="n">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="B969" s="60" t="inlineStr">
         <is>
-          <t>ときめきを、あなたに。</t>
+          <t>満足を、あなたに。</t>
         </is>
       </c>
       <c r="C969" s="61" t="inlineStr">
@@ -22985,11 +22985,11 @@
       </c>
       <c r="D969" s="62" t="inlineStr">
         <is>
-          <t>ときめき</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E969" s="63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="970" ht="19" customHeight="1">
@@ -22998,7 +22998,7 @@
       </c>
       <c r="B970" s="60" t="inlineStr">
         <is>
-          <t>ときめきを、もっと。</t>
+          <t>満足を、もっと。</t>
         </is>
       </c>
       <c r="C970" s="61" t="inlineStr">
@@ -23008,11 +23008,11 @@
       </c>
       <c r="D970" s="62" t="inlineStr">
         <is>
-          <t>ときめき</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E970" s="63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="971" ht="19" customHeight="1">
@@ -23021,7 +23021,7 @@
       </c>
       <c r="B971" s="60" t="inlineStr">
         <is>
-          <t>満足を、あなたに。</t>
+          <t>豊かさを、あなたに。</t>
         </is>
       </c>
       <c r="C971" s="61" t="inlineStr">
@@ -23031,11 +23031,11 @@
       </c>
       <c r="D971" s="62" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E971" s="63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="972" ht="19" customHeight="1">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="B972" s="60" t="inlineStr">
         <is>
-          <t>満足を、もっと。</t>
+          <t>豊かさを、もっと。</t>
         </is>
       </c>
       <c r="C972" s="61" t="inlineStr">
@@ -23054,11 +23054,11 @@
       </c>
       <c r="D972" s="62" t="inlineStr">
         <is>
-          <t>満足</t>
+          <t>豊かさ</t>
         </is>
       </c>
       <c r="E972" s="63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="973" ht="19" customHeight="1">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="B973" s="60" t="inlineStr">
         <is>
-          <t>豊かさを、あなたに。</t>
+          <t>感動を、あなたに。</t>
         </is>
       </c>
       <c r="C973" s="61" t="inlineStr">
@@ -23077,11 +23077,11 @@
       </c>
       <c r="D973" s="62" t="inlineStr">
         <is>
-          <t>豊かさ</t>
+          <t>感動</t>
         </is>
       </c>
       <c r="E973" s="63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="974" ht="19" customHeight="1">
@@ -23090,7 +23090,7 @@
       </c>
       <c r="B974" s="60" t="inlineStr">
         <is>
-          <t>豊かさを、もっと。</t>
+          <t>感動を、もっと。</t>
         </is>
       </c>
       <c r="C974" s="61" t="inlineStr">
@@ -23100,11 +23100,11 @@
       </c>
       <c r="D974" s="62" t="inlineStr">
         <is>
-          <t>豊かさ</t>
+          <t>感動</t>
         </is>
       </c>
       <c r="E974" s="63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="975" ht="19" customHeight="1">
@@ -23113,7 +23113,7 @@
       </c>
       <c r="B975" s="60" t="inlineStr">
         <is>
-          <t>感動を、あなたに。</t>
+          <t>うれしさを、あなたに。</t>
         </is>
       </c>
       <c r="C975" s="61" t="inlineStr">
@@ -23123,11 +23123,11 @@
       </c>
       <c r="D975" s="62" t="inlineStr">
         <is>
-          <t>感動</t>
+          <t>うれしさ</t>
         </is>
       </c>
       <c r="E975" s="63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="976" ht="19" customHeight="1">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="B976" s="60" t="inlineStr">
         <is>
-          <t>感動を、もっと。</t>
+          <t>うれしさを、もっと。</t>
         </is>
       </c>
       <c r="C976" s="61" t="inlineStr">
@@ -23146,11 +23146,11 @@
       </c>
       <c r="D976" s="62" t="inlineStr">
         <is>
-          <t>感動</t>
+          <t>うれしさ</t>
         </is>
       </c>
       <c r="E976" s="63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="977" ht="19" customHeight="1">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="B977" s="60" t="inlineStr">
         <is>
-          <t>うれしさを、あなたに。</t>
+          <t>ぬくもりを、あなたに。</t>
         </is>
       </c>
       <c r="C977" s="61" t="inlineStr">
@@ -23169,7 +23169,7 @@
       </c>
       <c r="D977" s="62" t="inlineStr">
         <is>
-          <t>うれしさ</t>
+          <t>ぬくもり</t>
         </is>
       </c>
       <c r="E977" s="63" t="n">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="B978" s="60" t="inlineStr">
         <is>
-          <t>うれしさを、もっと。</t>
+          <t>ぬくもりを、もっと。</t>
         </is>
       </c>
       <c r="C978" s="61" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="D978" s="62" t="inlineStr">
         <is>
-          <t>うれしさ</t>
+          <t>ぬくもり</t>
         </is>
       </c>
       <c r="E978" s="63" t="n">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="B979" s="60" t="inlineStr">
         <is>
-          <t>ぬくもりを、あなたに。</t>
+          <t>ゆとりを、あなたに。</t>
         </is>
       </c>
       <c r="C979" s="61" t="inlineStr">
@@ -23215,11 +23215,11 @@
       </c>
       <c r="D979" s="62" t="inlineStr">
         <is>
-          <t>ぬくもり</t>
+          <t>ゆとり</t>
         </is>
       </c>
       <c r="E979" s="63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="980" ht="19" customHeight="1">
@@ -23228,7 +23228,7 @@
       </c>
       <c r="B980" s="60" t="inlineStr">
         <is>
-          <t>ぬくもりを、もっと。</t>
+          <t>ゆとりを、もっと。</t>
         </is>
       </c>
       <c r="C980" s="61" t="inlineStr">
@@ -23238,11 +23238,11 @@
       </c>
       <c r="D980" s="62" t="inlineStr">
         <is>
-          <t>ぬくもり</t>
+          <t>ゆとり</t>
         </is>
       </c>
       <c r="E980" s="63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="981" ht="19" customHeight="1">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="B981" s="60" t="inlineStr">
         <is>
-          <t>ゆとりを、あなたに。</t>
+          <t>安心を、あなたに。</t>
         </is>
       </c>
       <c r="C981" s="61" t="inlineStr">
@@ -23261,11 +23261,11 @@
       </c>
       <c r="D981" s="62" t="inlineStr">
         <is>
-          <t>ゆとり</t>
+          <t>安心</t>
         </is>
       </c>
       <c r="E981" s="63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="982" ht="19" customHeight="1">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="B982" s="60" t="inlineStr">
         <is>
-          <t>ゆとりを、もっと。</t>
+          <t>安心を、もっと。</t>
         </is>
       </c>
       <c r="C982" s="61" t="inlineStr">
@@ -23284,11 +23284,11 @@
       </c>
       <c r="D982" s="62" t="inlineStr">
         <is>
-          <t>ゆとり</t>
+          <t>安心</t>
         </is>
       </c>
       <c r="E982" s="63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="983" ht="19" customHeight="1">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="B983" s="60" t="inlineStr">
         <is>
-          <t>安心を、あなたに。</t>
+          <t>ハッピーを、あなたに。</t>
         </is>
       </c>
       <c r="C983" s="61" t="inlineStr">
@@ -23307,11 +23307,11 @@
       </c>
       <c r="D983" s="62" t="inlineStr">
         <is>
-          <t>安心</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E983" s="63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="984" ht="19" customHeight="1">
@@ -23320,7 +23320,7 @@
       </c>
       <c r="B984" s="60" t="inlineStr">
         <is>
-          <t>安心を、もっと。</t>
+          <t>ハッピーを、もっと。</t>
         </is>
       </c>
       <c r="C984" s="61" t="inlineStr">
@@ -23330,11 +23330,11 @@
       </c>
       <c r="D984" s="62" t="inlineStr">
         <is>
-          <t>安心</t>
+          <t>ハッピー</t>
         </is>
       </c>
       <c r="E984" s="63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="985" ht="19" customHeight="1">
@@ -23343,7 +23343,7 @@
       </c>
       <c r="B985" s="60" t="inlineStr">
         <is>
-          <t>ハッピーを、あなたに。</t>
+          <t>わくわくを、あなたに。</t>
         </is>
       </c>
       <c r="C985" s="61" t="inlineStr">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="D985" s="62" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>わくわく</t>
         </is>
       </c>
       <c r="E985" s="63" t="n">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="B986" s="60" t="inlineStr">
         <is>
-          <t>ハッピーを、もっと。</t>
+          <t>わくわくを、もっと。</t>
         </is>
       </c>
       <c r="C986" s="61" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="D986" s="62" t="inlineStr">
         <is>
-          <t>ハッピー</t>
+          <t>わくわく</t>
         </is>
       </c>
       <c r="E986" s="63" t="n">
@@ -23596,7 +23596,7 @@
       </c>
       <c r="B996" s="40" t="inlineStr">
         <is>
-          <t>笑顔で、選ばれる。</t>
+          <t>喜びで、選ばれる。</t>
         </is>
       </c>
       <c r="C996" s="41" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="D996" s="42" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E996" s="43" t="n">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="B997" s="45" t="inlineStr">
         <is>
-          <t>笑顔で、売れていく。</t>
+          <t>喜びで、売れていく。</t>
         </is>
       </c>
       <c r="C997" s="46" t="inlineStr">
@@ -23629,7 +23629,7 @@
       </c>
       <c r="D997" s="47" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E997" s="48" t="n">
@@ -23642,7 +23642,7 @@
       </c>
       <c r="B998" s="60" t="inlineStr">
         <is>
-          <t>笑顔を、ぜんぶ。</t>
+          <t>喜びを、ぜんぶ。</t>
         </is>
       </c>
       <c r="C998" s="61" t="inlineStr">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="D998" s="62" t="inlineStr">
         <is>
-          <t>笑顔</t>
+          <t>喜び</t>
         </is>
       </c>
       <c r="E998" s="63" t="n">
@@ -23665,7 +23665,7 @@
       </c>
       <c r="B999" s="40" t="inlineStr">
         <is>
-          <t>喜びで、選ばれる。</t>
+          <t>満足で、選ばれる。</t>
         </is>
       </c>
       <c r="C999" s="41" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="D999" s="42" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E999" s="43" t="n">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="B1000" s="45" t="inlineStr">
         <is>
-          <t>喜びで、売れていく。</t>
+          <t>満足で、売れていく。</t>
         </is>
       </c>
       <c r="C1000" s="46" t="inlineStr">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="D1000" s="47" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E1000" s="48" t="n">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="B1001" s="60" t="inlineStr">
         <is>
-          <t>喜びを、ぜんぶ。</t>
+          <t>満足を、ぜんぶ。</t>
         </is>
       </c>
       <c r="C1001" s="61" t="inlineStr">
@@ -23721,7 +23721,7 @@
       </c>
       <c r="D1001" s="62" t="inlineStr">
         <is>
-          <t>喜び</t>
+          <t>満足</t>
         </is>
       </c>
       <c r="E1001" s="63" t="n">
